--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2739E8-A615-4C39-8DA3-404CFC627142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CA07F-DF8D-4581-809B-F2D4A014C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Working_Data" sheetId="4" r:id="rId1"/>
-    <sheet name="Raw_Employee_Data" sheetId="1" r:id="rId2"/>
-    <sheet name="Lookup_Departments" sheetId="2" r:id="rId3"/>
-    <sheet name="Lookup_Performance" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId1"/>
+    <sheet name="Working_Data" sheetId="4" r:id="rId2"/>
+    <sheet name="Raw_Employee_Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Lookup_Departments" sheetId="2" r:id="rId4"/>
+    <sheet name="Lookup_Performance" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="287">
   <si>
     <t>Emp ID</t>
   </si>
@@ -839,6 +843,12 @@
     <t>ACTIVE</t>
   </si>
   <si>
+    <t>LEFT</t>
+  </si>
+  <si>
+    <t>RESIGNED</t>
+  </si>
+  <si>
     <t>Unknown</t>
   </si>
   <si>
@@ -873,6 +883,27 @@
   </si>
   <si>
     <t>Eligible_Bonus_Amount</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Average Salary</t>
+  </si>
+  <si>
+    <t>HeadCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        Headcount &amp; Average Salary by Department</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Attrition Rate</t>
+  </si>
+  <si>
+    <t>Attrition rate</t>
   </si>
 </sst>
 </file>
@@ -884,7 +915,7 @@
     <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="&quot;₦&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,12 +929,26 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -938,10 +983,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -967,22 +1013,88 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="&quot;₦&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -993,6 +1105,3004 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="USER" refreshedDate="46213.730153356482" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="150" xr:uid="{E70A63EC-7F06-4E42-8492-733C8B086761}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="13">
+    <cacheField name="Cleaned EMP ID" numFmtId="2">
+      <sharedItems count="150">
+        <s v="EMP127"/>
+        <s v="EMP046"/>
+        <s v="EMP134"/>
+        <s v="EMP139"/>
+        <s v="EMP112"/>
+        <s v="EMP030"/>
+        <s v="EMP096"/>
+        <s v="EMP098"/>
+        <s v="EMP095"/>
+        <s v="EMP140"/>
+        <s v="EMP020"/>
+        <s v="EMP057"/>
+        <s v="EMP016"/>
+        <s v="EMP070"/>
+        <s v="EMP025"/>
+        <s v="EMP031"/>
+        <s v="EMP126"/>
+        <s v="EMP109"/>
+        <s v="EMP066"/>
+        <s v="EMP120"/>
+        <s v="EMP019"/>
+        <s v="EMP013"/>
+        <s v="EMP010"/>
+        <s v="EMP032"/>
+        <s v="EMP082"/>
+        <s v="EMP052"/>
+        <s v="EMP129"/>
+        <s v="EMP146"/>
+        <s v="EMP099"/>
+        <s v="EMP015"/>
+        <s v="EMP076"/>
+        <s v="EMP137"/>
+        <s v="EMP056"/>
+        <s v="EMP125"/>
+        <s v="EMP085"/>
+        <s v="EMP106"/>
+        <s v="EMP043"/>
+        <s v="EMP068"/>
+        <s v="EMP128"/>
+        <s v="EMP027"/>
+        <s v="EMP136"/>
+        <s v="EMP079"/>
+        <s v="EMP149"/>
+        <s v="EMP037"/>
+        <s v="EMP077"/>
+        <s v="EMP023"/>
+        <s v="EMP133"/>
+        <s v="EMP141"/>
+        <s v="EMP012"/>
+        <s v="EMP080"/>
+        <s v="EMP069"/>
+        <s v="EMP150"/>
+        <s v="EMP028"/>
+        <s v="EMP087"/>
+        <s v="EMP119"/>
+        <s v="EMP042"/>
+        <s v="EMP005"/>
+        <s v="EMP033"/>
+        <s v="EMP061"/>
+        <s v="EMP102"/>
+        <s v="EMP067"/>
+        <s v="EMP017"/>
+        <s v="EMP123"/>
+        <s v="EMP011"/>
+        <s v="EMP091"/>
+        <s v="EMP145"/>
+        <s v="EMP001"/>
+        <s v="EMP113"/>
+        <s v="EMP065"/>
+        <s v="EMP045"/>
+        <s v="EMP083"/>
+        <s v="EMP029"/>
+        <s v="EMP041"/>
+        <s v="EMP026"/>
+        <s v="EMP024"/>
+        <s v="EMP111"/>
+        <s v="EMP040"/>
+        <s v="EMP086"/>
+        <s v="EMP124"/>
+        <s v="EMP132"/>
+        <s v="EMP048"/>
+        <s v="EMP114"/>
+        <s v="EMP062"/>
+        <s v="EMP074"/>
+        <s v="EMP034"/>
+        <s v="EMP105"/>
+        <s v="EMP118"/>
+        <s v="EMP063"/>
+        <s v="EMP094"/>
+        <s v="EMP097"/>
+        <s v="EMP054"/>
+        <s v="EMP006"/>
+        <s v="EMP110"/>
+        <s v="EMP147"/>
+        <s v="EMP050"/>
+        <s v="EMP036"/>
+        <s v="EMP081"/>
+        <s v="EMP078"/>
+        <s v="EMP035"/>
+        <s v="EMP047"/>
+        <s v="EMP008"/>
+        <s v="EMP044"/>
+        <s v="EMP071"/>
+        <s v="EMP115"/>
+        <s v="EMP092"/>
+        <s v="EMP084"/>
+        <s v="EMP142"/>
+        <s v="EMP143"/>
+        <s v="EMP090"/>
+        <s v="EMP009"/>
+        <s v="EMP014"/>
+        <s v="EMP060"/>
+        <s v="EMP135"/>
+        <s v="EMP004"/>
+        <s v="EMP018"/>
+        <s v="EMP039"/>
+        <s v="EMP073"/>
+        <s v="EMP138"/>
+        <s v="EMP007"/>
+        <s v="EMP144"/>
+        <s v="EMP101"/>
+        <s v="EMP003"/>
+        <s v="EMP121"/>
+        <s v="EMP064"/>
+        <s v="EMP116"/>
+        <s v="EMP055"/>
+        <s v="EMP108"/>
+        <s v="EMP051"/>
+        <s v="EMP059"/>
+        <s v="EMP049"/>
+        <s v="EMP089"/>
+        <s v="EMP022"/>
+        <s v="EMP058"/>
+        <s v="EMP130"/>
+        <s v="EMP038"/>
+        <s v="EMP148"/>
+        <s v="EMP002"/>
+        <s v="EMP053"/>
+        <s v="EMP131"/>
+        <s v="EMP104"/>
+        <s v="EMP100"/>
+        <s v="EMP117"/>
+        <s v="EMP088"/>
+        <s v="EMP075"/>
+        <s v="EMP122"/>
+        <s v="EMP021"/>
+        <s v="EMP072"/>
+        <s v="EMP107"/>
+        <s v="EMP093"/>
+        <s v="EMP103"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Cleaned First_Name" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cleaned Last_Name" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Full_Name" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Department_Name" numFmtId="49">
+      <sharedItems count="6">
+        <s v="Information Technology"/>
+        <s v="Marketing"/>
+        <s v="Finance"/>
+        <s v="Operations"/>
+        <s v="Sales"/>
+        <s v="Human Resources"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Cleaned Dept_Code" numFmtId="2">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Cleaned Hire_Date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2015-01-04T00:00:00" maxDate="2023-12-13T00:00:00"/>
+    </cacheField>
+    <cacheField name="Year_of_Service" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="11"/>
+    </cacheField>
+    <cacheField name="Cleaned Salary" numFmtId="168">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45196" maxValue="118947"/>
+    </cacheField>
+    <cacheField name="Cleaned Perf_Score" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="30" maxValue="99"/>
+    </cacheField>
+    <cacheField name="Performance_Band" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Eligible_Bonus_Amount" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.12"/>
+    </cacheField>
+    <cacheField name="Cleaned Employment_Status" numFmtId="49">
+      <sharedItems count="3">
+        <s v="ACTIVE"/>
+        <s v="LEFT"/>
+        <s v="RESIGNED"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="150">
+  <r>
+    <x v="0"/>
+    <s v="Emily"/>
+    <s v="Brown"/>
+    <s v="Emily Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2017-12-24T00:00:00"/>
+    <n v="8"/>
+    <n v="50361"/>
+    <n v="52"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Richard"/>
+    <s v="Hernandez"/>
+    <s v="Richard Hernandez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2022-04-08T00:00:00"/>
+    <n v="4"/>
+    <n v="112673"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Emily"/>
+    <s v="Gonzalez"/>
+    <s v="Emily Gonzalez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2016-03-02T00:00:00"/>
+    <n v="10"/>
+    <n v="114425"/>
+    <n v="54"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="John"/>
+    <s v="Martinez"/>
+    <s v="John Martinez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2023-07-03T00:00:00"/>
+    <n v="3"/>
+    <n v="103831"/>
+    <n v="70"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Thomas"/>
+    <s v="Smith"/>
+    <s v="Thomas Smith"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-02-20T00:00:00"/>
+    <n v="3"/>
+    <n v="73785"/>
+    <n v="40"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Emily"/>
+    <s v="Johnson"/>
+    <s v="Emily Johnson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2020-03-02T00:00:00"/>
+    <n v="6"/>
+    <n v="115882"/>
+    <n v="49"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="John"/>
+    <s v="Wilson"/>
+    <s v="John Wilson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2023-12-12T00:00:00"/>
+    <n v="2"/>
+    <n v="59980"/>
+    <n v="70"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Jessica"/>
+    <s v="Smith"/>
+    <s v="Jessica Smith"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2020-12-09T00:00:00"/>
+    <n v="5"/>
+    <n v="68728"/>
+    <n v="45"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Unknown"/>
+    <s v="Rodriguez"/>
+    <s v="Unknown Rodriguez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2018-01-07T00:00:00"/>
+    <n v="8"/>
+    <n v="102139"/>
+    <n v="79"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Michael"/>
+    <s v="Martinez"/>
+    <s v="Michael Martinez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2016-11-02T00:00:00"/>
+    <n v="9"/>
+    <n v="94998"/>
+    <n v="58"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Emily"/>
+    <s v="Miller"/>
+    <s v="Emily Miller"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2020-03-21T00:00:00"/>
+    <n v="6"/>
+    <n v="118635"/>
+    <n v="49"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Emily"/>
+    <s v="Hernandez"/>
+    <s v="Emily Hernandez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2016-02-25T00:00:00"/>
+    <n v="10"/>
+    <n v="76918"/>
+    <n v="62"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Jane"/>
+    <s v="Williams"/>
+    <s v="Jane Williams"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2021-06-17T00:00:00"/>
+    <n v="5"/>
+    <n v="61408"/>
+    <n v="48"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Jane"/>
+    <s v="Miller"/>
+    <s v="Jane Miller"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2020-06-19T00:00:00"/>
+    <n v="6"/>
+    <n v="99990"/>
+    <n v="54"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Robert"/>
+    <s v="Jones"/>
+    <s v="Robert Jones"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2019-12-21T00:00:00"/>
+    <n v="6"/>
+    <n v="80385"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Thomas"/>
+    <s v="Rodriguez"/>
+    <s v="Thomas Rodriguez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2023-08-31T00:00:00"/>
+    <n v="2"/>
+    <n v="65290"/>
+    <n v="77"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Emily"/>
+    <s v="Davis"/>
+    <s v="Emily Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2015-11-29T00:00:00"/>
+    <n v="10"/>
+    <n v="105765"/>
+    <n v="42"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="James"/>
+    <s v="Martinez"/>
+    <s v="James Martinez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2017-06-13T00:00:00"/>
+    <n v="9"/>
+    <n v="102921"/>
+    <n v="49"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Ashley"/>
+    <s v="Lopez"/>
+    <s v="Ashley Lopez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2018-05-15T00:00:00"/>
+    <n v="8"/>
+    <n v="73984"/>
+    <n v="62"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Amanda"/>
+    <s v="Gonzalez"/>
+    <s v="Amanda Gonzalez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2016-07-24T00:00:00"/>
+    <n v="9"/>
+    <n v="80014.258064516136"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Michael"/>
+    <s v="Hernandez"/>
+    <s v="Michael Hernandez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2017-12-07T00:00:00"/>
+    <n v="8"/>
+    <n v="118527"/>
+    <n v="75"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Richard"/>
+    <s v="Hernandez"/>
+    <s v="Richard Hernandez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2021-06-06T00:00:00"/>
+    <n v="5"/>
+    <n v="107871"/>
+    <n v="50"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Michael"/>
+    <s v="Rodriguez"/>
+    <s v="Michael Rodriguez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2022-09-11T00:00:00"/>
+    <n v="3"/>
+    <n v="93956"/>
+    <n v="88"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Jessica"/>
+    <s v="Johnson"/>
+    <s v="Jessica Johnson"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2016-07-14T00:00:00"/>
+    <n v="9"/>
+    <n v="100851"/>
+    <n v="50"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="Ashley"/>
+    <s v="Williams"/>
+    <s v="Ashley Williams"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2022-06-16T00:00:00"/>
+    <n v="4"/>
+    <n v="68655"/>
+    <n v="64"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="Unknown"/>
+    <s v="Williams"/>
+    <s v="Unknown Williams"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2023-07-27T00:00:00"/>
+    <n v="2"/>
+    <n v="81205"/>
+    <n v="32"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="John"/>
+    <s v="Wilson"/>
+    <s v="John Wilson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2019-09-24T00:00:00"/>
+    <n v="6"/>
+    <n v="77610"/>
+    <n v="59"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="Thomas"/>
+    <s v="Rodriguez"/>
+    <s v="Thomas Rodriguez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2022-07-23T00:00:00"/>
+    <n v="3"/>
+    <n v="50873"/>
+    <n v="88"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="Michael"/>
+    <s v="Wilson"/>
+    <s v="Michael Wilson"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2018-05-13T00:00:00"/>
+    <n v="8"/>
+    <n v="85312"/>
+    <n v="90"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="John"/>
+    <s v="Rodriguez"/>
+    <s v="John Rodriguez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2015-07-17T00:00:00"/>
+    <n v="10"/>
+    <n v="87282.34782608696"/>
+    <n v="66"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="Thomas"/>
+    <s v="Hernandez"/>
+    <s v="Thomas Hernandez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2015-08-05T00:00:00"/>
+    <n v="10"/>
+    <n v="97055"/>
+    <n v="68"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="Michael"/>
+    <s v="Johnson"/>
+    <s v="Michael Johnson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-09-26T00:00:00"/>
+    <n v="2"/>
+    <n v="66069"/>
+    <n v="80"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="Sarah"/>
+    <s v="Brown"/>
+    <s v="Sarah Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2019-06-10T00:00:00"/>
+    <n v="7"/>
+    <n v="90157"/>
+    <n v="72"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="Jane"/>
+    <s v="Martinez"/>
+    <s v="Jane Martinez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2022-01-17T00:00:00"/>
+    <n v="4"/>
+    <n v="59899"/>
+    <n v="58"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="Emily"/>
+    <s v="Jones"/>
+    <s v="Emily Jones"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2017-07-03T00:00:00"/>
+    <n v="9"/>
+    <n v="113389"/>
+    <n v="78"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="Unknown"/>
+    <s v="Brown"/>
+    <s v="Unknown Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2015-09-01T00:00:00"/>
+    <n v="10"/>
+    <n v="102691"/>
+    <n v="30"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="John"/>
+    <s v="Wilson"/>
+    <s v="John Wilson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2022-08-03T00:00:00"/>
+    <n v="3"/>
+    <n v="111845"/>
+    <n v="52"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="Melissa"/>
+    <s v="Brown"/>
+    <s v="Melissa Brown"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2022-06-29T00:00:00"/>
+    <n v="4"/>
+    <n v="69219"/>
+    <n v="98"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="Michael"/>
+    <s v="Smith"/>
+    <s v="Michael Smith"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2020-04-28T00:00:00"/>
+    <n v="6"/>
+    <n v="87938.5"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="Sarah"/>
+    <s v="Miller"/>
+    <s v="Sarah Miller"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2017-09-09T00:00:00"/>
+    <n v="8"/>
+    <n v="57514"/>
+    <n v="80"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="Emily"/>
+    <s v="Wilson"/>
+    <s v="Emily Wilson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2018-03-22T00:00:00"/>
+    <n v="8"/>
+    <n v="86245"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="David"/>
+    <s v="Hernandez"/>
+    <s v="David Hernandez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2020-05-07T00:00:00"/>
+    <n v="6"/>
+    <n v="52407"/>
+    <n v="71"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="James"/>
+    <s v="Smith"/>
+    <s v="James Smith"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2019-03-25T00:00:00"/>
+    <n v="7"/>
+    <n v="66606"/>
+    <n v="55"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="Sarah"/>
+    <s v="Williams"/>
+    <s v="Sarah Williams"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2019-08-09T00:00:00"/>
+    <n v="6"/>
+    <n v="81896"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="Amanda"/>
+    <s v="Lopez"/>
+    <s v="Amanda Lopez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2016-07-14T00:00:00"/>
+    <n v="9"/>
+    <n v="78402"/>
+    <n v="79"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Thomas"/>
+    <s v="Lopez"/>
+    <s v="Thomas Lopez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2016-10-04T00:00:00"/>
+    <n v="9"/>
+    <n v="105498"/>
+    <n v="54"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="Melissa"/>
+    <s v="Johnson"/>
+    <s v="Melissa Johnson"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2019-07-10T00:00:00"/>
+    <n v="7"/>
+    <n v="91749"/>
+    <n v="76"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="Amanda"/>
+    <s v="Johnson"/>
+    <s v="Amanda Johnson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2021-08-29T00:00:00"/>
+    <n v="4"/>
+    <n v="99935"/>
+    <n v="72"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="John"/>
+    <s v="Davis"/>
+    <s v="John Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2017-01-26T00:00:00"/>
+    <n v="9"/>
+    <n v="83531"/>
+    <n v="84"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <s v="James"/>
+    <s v="Johnson"/>
+    <s v="James Johnson"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2020-05-30T00:00:00"/>
+    <n v="6"/>
+    <n v="75023"/>
+    <n v="30"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <s v="Jane"/>
+    <s v="Davis"/>
+    <s v="Jane Davis"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2022-02-20T00:00:00"/>
+    <n v="4"/>
+    <n v="93290"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <s v="Richard"/>
+    <s v="Davis"/>
+    <s v="Richard Davis"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2016-09-15T00:00:00"/>
+    <n v="9"/>
+    <n v="115527"/>
+    <n v="53"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <s v="Thomas"/>
+    <s v="Rodriguez"/>
+    <s v="Thomas Rodriguez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2019-07-10T00:00:00"/>
+    <n v="7"/>
+    <n v="55920"/>
+    <n v="63"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <s v="Emily"/>
+    <s v="Johnson"/>
+    <s v="Emily Johnson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2018-12-30T00:00:00"/>
+    <n v="7"/>
+    <n v="80189"/>
+    <n v="84"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <s v="Emily"/>
+    <s v="Garcia"/>
+    <s v="Emily Garcia"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2020-12-24T00:00:00"/>
+    <n v="5"/>
+    <n v="118947"/>
+    <n v="30"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <s v="Jane"/>
+    <s v="Anderson"/>
+    <s v="Jane Anderson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-07-05T00:00:00"/>
+    <n v="3"/>
+    <n v="80014.258064516136"/>
+    <n v="96"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <s v="Thomas"/>
+    <s v="Garcia"/>
+    <s v="Thomas Garcia"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2020-11-13T00:00:00"/>
+    <n v="5"/>
+    <n v="79786.666666666672"/>
+    <n v="54"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <s v="David"/>
+    <s v="Martinez"/>
+    <s v="David Martinez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2018-07-02T00:00:00"/>
+    <n v="8"/>
+    <n v="91655"/>
+    <n v="75"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <s v="Emily"/>
+    <s v="Brown"/>
+    <s v="Emily Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-11-25T00:00:00"/>
+    <n v="2"/>
+    <n v="49435"/>
+    <n v="95"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <s v="Emily"/>
+    <s v="Wilson"/>
+    <s v="Emily Wilson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2023-10-18T00:00:00"/>
+    <n v="2"/>
+    <n v="110381"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <s v="Michael"/>
+    <s v="Anderson"/>
+    <s v="Michael Anderson"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2020-09-05T00:00:00"/>
+    <n v="5"/>
+    <n v="114748"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <s v="Robert"/>
+    <s v="Johnson"/>
+    <s v="Robert Johnson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2017-03-06T00:00:00"/>
+    <n v="9"/>
+    <n v="63302"/>
+    <n v="33"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <s v="Robert"/>
+    <s v="Miller"/>
+    <s v="Robert Miller"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2015-04-28T00:00:00"/>
+    <n v="11"/>
+    <n v="75519"/>
+    <n v="91"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <s v="Jane"/>
+    <s v="Davis"/>
+    <s v="Jane Davis"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2017-04-13T00:00:00"/>
+    <n v="9"/>
+    <n v="103891"/>
+    <n v="64"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <s v="Thomas"/>
+    <s v="Davis"/>
+    <s v="Thomas Davis"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2022-09-23T00:00:00"/>
+    <n v="3"/>
+    <n v="79786.666666666672"/>
+    <n v="80"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <s v="Thomas"/>
+    <s v="Jones"/>
+    <s v="Thomas Jones"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2016-11-11T00:00:00"/>
+    <n v="9"/>
+    <n v="50936"/>
+    <n v="46"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <s v="Michael"/>
+    <s v="Miller"/>
+    <s v="Michael Miller"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2017-03-24T00:00:00"/>
+    <n v="9"/>
+    <n v="111240"/>
+    <n v="99"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <s v="Richard"/>
+    <s v="Gonzalez"/>
+    <s v="Richard Gonzalez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2019-05-05T00:00:00"/>
+    <n v="7"/>
+    <n v="51567"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <s v="Melissa"/>
+    <s v="Williams"/>
+    <s v="Melissa Williams"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2021-07-25T00:00:00"/>
+    <n v="4"/>
+    <n v="85649.941176470587"/>
+    <n v="87"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <s v="Robert"/>
+    <s v="Miller"/>
+    <s v="Robert Miller"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2017-09-30T00:00:00"/>
+    <n v="8"/>
+    <n v="55270"/>
+    <n v="36"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <s v="William"/>
+    <s v="Garcia"/>
+    <s v="William Garcia"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2015-07-07T00:00:00"/>
+    <n v="11"/>
+    <n v="65235"/>
+    <n v="87"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <s v="John"/>
+    <s v="Gonzalez"/>
+    <s v="John Gonzalez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2018-07-02T00:00:00"/>
+    <n v="8"/>
+    <n v="87282.34782608696"/>
+    <n v="97"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <s v="James"/>
+    <s v="Gonzalez"/>
+    <s v="James Gonzalez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2022-09-15T00:00:00"/>
+    <n v="3"/>
+    <n v="87282.34782608696"/>
+    <n v="72"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <s v="Jane"/>
+    <s v="Gonzalez"/>
+    <s v="Jane Gonzalez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2015-09-02T00:00:00"/>
+    <n v="10"/>
+    <n v="87282.34782608696"/>
+    <n v="65"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <s v="David"/>
+    <s v="Wilson"/>
+    <s v="David Wilson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2016-10-11T00:00:00"/>
+    <n v="9"/>
+    <n v="48823"/>
+    <n v="91"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <s v="Jane"/>
+    <s v="Gonzalez"/>
+    <s v="Jane Gonzalez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2019-04-20T00:00:00"/>
+    <n v="7"/>
+    <n v="45196"/>
+    <n v="67"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <s v="Jane"/>
+    <s v="Rodriguez"/>
+    <s v="Jane Rodriguez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2017-02-19T00:00:00"/>
+    <n v="9"/>
+    <n v="86246"/>
+    <n v="34"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <s v="Emily"/>
+    <s v="Miller"/>
+    <s v="Emily Miller"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2021-07-09T00:00:00"/>
+    <n v="5"/>
+    <n v="70359"/>
+    <n v="78"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <s v="Sarah"/>
+    <s v="Miller"/>
+    <s v="Sarah Miller"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2019-05-14T00:00:00"/>
+    <n v="7"/>
+    <n v="85508.166666666672"/>
+    <n v="61"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <s v="Jessica"/>
+    <s v="Garcia"/>
+    <s v="Jessica Garcia"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2015-11-22T00:00:00"/>
+    <n v="10"/>
+    <n v="86480"/>
+    <n v="74"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <s v="Richard"/>
+    <s v="Smith"/>
+    <s v="Richard Smith"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2018-09-29T00:00:00"/>
+    <n v="7"/>
+    <n v="47694"/>
+    <n v="94"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <s v="Melissa"/>
+    <s v="Wilson"/>
+    <s v="Melissa Wilson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-09-02T00:00:00"/>
+    <n v="2"/>
+    <n v="83724"/>
+    <n v="80"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <s v="Thomas"/>
+    <s v="Williams"/>
+    <s v="Thomas Williams"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2022-07-17T00:00:00"/>
+    <n v="3"/>
+    <n v="98299"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <s v="David"/>
+    <s v="Williams"/>
+    <s v="David Williams"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2021-02-07T00:00:00"/>
+    <n v="5"/>
+    <n v="87938.5"/>
+    <n v="75"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <s v="John"/>
+    <s v="Johnson"/>
+    <s v="John Johnson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-04-10T00:00:00"/>
+    <n v="3"/>
+    <n v="52287"/>
+    <n v="81"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <s v="Richard"/>
+    <s v="Gonzalez"/>
+    <s v="Richard Gonzalez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2020-08-30T00:00:00"/>
+    <n v="5"/>
+    <n v="82633"/>
+    <n v="61"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <s v="Melissa"/>
+    <s v="Anderson"/>
+    <s v="Melissa Anderson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2021-08-14T00:00:00"/>
+    <n v="4"/>
+    <n v="46508"/>
+    <n v="68"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <s v="Emily"/>
+    <s v="Gonzalez"/>
+    <s v="Emily Gonzalez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2019-11-27T00:00:00"/>
+    <n v="6"/>
+    <n v="86232"/>
+    <n v="70"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <s v="Jane"/>
+    <s v="Davis"/>
+    <s v="Jane Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2017-05-25T00:00:00"/>
+    <n v="9"/>
+    <n v="77545"/>
+    <n v="98"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <s v="William"/>
+    <s v="Gonzalez"/>
+    <s v="William Gonzalez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2018-12-02T00:00:00"/>
+    <n v="7"/>
+    <n v="68683"/>
+    <n v="34"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <s v="Thomas"/>
+    <s v="Jones"/>
+    <s v="Thomas Jones"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2019-06-23T00:00:00"/>
+    <n v="7"/>
+    <n v="83932"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <s v="Jessica"/>
+    <s v="Anderson"/>
+    <s v="Jessica Anderson"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2015-10-27T00:00:00"/>
+    <n v="10"/>
+    <n v="56073"/>
+    <n v="48"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <s v="Melissa"/>
+    <s v="Johnson"/>
+    <s v="Melissa Johnson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2018-06-19T00:00:00"/>
+    <n v="8"/>
+    <n v="88056"/>
+    <n v="90"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <s v="Thomas"/>
+    <s v="Miller"/>
+    <s v="Thomas Miller"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2018-01-12T00:00:00"/>
+    <n v="8"/>
+    <n v="67414"/>
+    <n v="57"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <s v="William"/>
+    <s v="Gonzalez"/>
+    <s v="William Gonzalez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2015-01-04T00:00:00"/>
+    <n v="11"/>
+    <n v="115288"/>
+    <n v="79"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <s v="Unknown"/>
+    <s v="Smith"/>
+    <s v="Unknown Smith"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2018-12-05T00:00:00"/>
+    <n v="7"/>
+    <n v="80140"/>
+    <n v="66"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <s v="John"/>
+    <s v="Johnson"/>
+    <s v="John Johnson"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2021-10-13T00:00:00"/>
+    <n v="4"/>
+    <n v="73087"/>
+    <n v="84"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <s v="Jane"/>
+    <s v="Johnson"/>
+    <s v="Jane Johnson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2020-09-07T00:00:00"/>
+    <n v="5"/>
+    <n v="95292"/>
+    <n v="61"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <s v="John"/>
+    <s v="Jones"/>
+    <s v="John Jones"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2019-08-03T00:00:00"/>
+    <n v="6"/>
+    <n v="80014.258064516136"/>
+    <n v="58"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="99"/>
+    <s v="Jane"/>
+    <s v="Lopez"/>
+    <s v="Jane Lopez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="11"/>
+    <n v="101750"/>
+    <n v="69"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <s v="Melissa"/>
+    <s v="Gonzalez"/>
+    <s v="Melissa Gonzalez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2017-02-19T00:00:00"/>
+    <n v="9"/>
+    <n v="82992"/>
+    <n v="34"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="101"/>
+    <s v="William"/>
+    <s v="Davis"/>
+    <s v="William Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2023-05-09T00:00:00"/>
+    <n v="3"/>
+    <n v="49942"/>
+    <n v="33"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="102"/>
+    <s v="John"/>
+    <s v="Smith"/>
+    <s v="John Smith"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2018-01-22T00:00:00"/>
+    <n v="8"/>
+    <n v="89060"/>
+    <n v="84"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="103"/>
+    <s v="James"/>
+    <s v="Gonzalez"/>
+    <s v="James Gonzalez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2020-02-18T00:00:00"/>
+    <n v="6"/>
+    <n v="53786"/>
+    <n v="79"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="104"/>
+    <s v="Emily"/>
+    <s v="Johnson"/>
+    <s v="Emily Johnson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2016-05-22T00:00:00"/>
+    <n v="10"/>
+    <n v="81167"/>
+    <n v="51"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="105"/>
+    <s v="William"/>
+    <s v="Williams"/>
+    <s v="William Williams"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2021-06-02T00:00:00"/>
+    <n v="5"/>
+    <n v="66688"/>
+    <n v="58"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="106"/>
+    <s v="James"/>
+    <s v="Jones"/>
+    <s v="James Jones"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2021-07-17T00:00:00"/>
+    <n v="4"/>
+    <n v="91672"/>
+    <n v="98"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="107"/>
+    <s v="Jessica"/>
+    <s v="Gonzalez"/>
+    <s v="Jessica Gonzalez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2016-11-13T00:00:00"/>
+    <n v="9"/>
+    <n v="77737"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="108"/>
+    <s v="Sarah"/>
+    <s v="Miller"/>
+    <s v="Sarah Miller"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2019-02-17T00:00:00"/>
+    <n v="7"/>
+    <n v="95686"/>
+    <n v="40"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="109"/>
+    <s v="Jessica"/>
+    <s v="Smith"/>
+    <s v="Jessica Smith"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2016-09-12T00:00:00"/>
+    <n v="9"/>
+    <n v="114681"/>
+    <n v="88"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="110"/>
+    <s v="Thomas"/>
+    <s v="Jones"/>
+    <s v="Thomas Jones"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2021-08-13T00:00:00"/>
+    <n v="4"/>
+    <n v="109121"/>
+    <n v="77"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="111"/>
+    <s v="Amanda"/>
+    <s v="Brown"/>
+    <s v="Amanda Brown"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2020-06-14T00:00:00"/>
+    <n v="6"/>
+    <n v="112791"/>
+    <n v="91"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="112"/>
+    <s v="Robert"/>
+    <s v="Martinez"/>
+    <s v="Robert Martinez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2022-07-05T00:00:00"/>
+    <n v="4"/>
+    <n v="118008"/>
+    <n v="36"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="113"/>
+    <s v="Thomas"/>
+    <s v="Miller"/>
+    <s v="Thomas Miller"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2016-10-07T00:00:00"/>
+    <n v="9"/>
+    <n v="74370"/>
+    <n v="72"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="114"/>
+    <s v="David"/>
+    <s v="Rodriguez"/>
+    <s v="David Rodriguez"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2022-04-23T00:00:00"/>
+    <n v="4"/>
+    <n v="77819"/>
+    <n v="87"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="115"/>
+    <s v="Jane"/>
+    <s v="Miller"/>
+    <s v="Jane Miller"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2017-10-05T00:00:00"/>
+    <n v="8"/>
+    <n v="48748"/>
+    <n v="71"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="116"/>
+    <s v="James"/>
+    <s v="Rodriguez"/>
+    <s v="James Rodriguez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2020-05-20T00:00:00"/>
+    <n v="6"/>
+    <n v="101997"/>
+    <n v="82"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="117"/>
+    <s v="Sarah"/>
+    <s v="Rodriguez"/>
+    <s v="Sarah Rodriguez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2023-04-20T00:00:00"/>
+    <n v="3"/>
+    <n v="115260"/>
+    <n v="79"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="118"/>
+    <s v="Sarah"/>
+    <s v="Wilson"/>
+    <s v="Sarah Wilson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2021-10-31T00:00:00"/>
+    <n v="4"/>
+    <n v="87282.34782608696"/>
+    <n v="83"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="119"/>
+    <s v="Melissa"/>
+    <s v="Brown"/>
+    <s v="Melissa Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2021-10-24T00:00:00"/>
+    <n v="4"/>
+    <n v="80014.258064516136"/>
+    <n v="38"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="120"/>
+    <s v="Robert"/>
+    <s v="Williams"/>
+    <s v="Robert Williams"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2017-08-09T00:00:00"/>
+    <n v="8"/>
+    <n v="87282.34782608696"/>
+    <n v="77"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="121"/>
+    <s v="Melissa"/>
+    <s v="Rodriguez"/>
+    <s v="Melissa Rodriguez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2023-01-04T00:00:00"/>
+    <n v="3"/>
+    <n v="60623"/>
+    <n v="49"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="122"/>
+    <s v="James"/>
+    <s v="Johnson"/>
+    <s v="James Johnson"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2020-08-10T00:00:00"/>
+    <n v="5"/>
+    <n v="68092"/>
+    <n v="69"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="123"/>
+    <s v="Michael"/>
+    <s v="Wilson"/>
+    <s v="Michael Wilson"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2022-04-02T00:00:00"/>
+    <n v="4"/>
+    <n v="88155"/>
+    <n v="76"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="124"/>
+    <s v="William"/>
+    <s v="Jones"/>
+    <s v="William Jones"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2018-03-24T00:00:00"/>
+    <n v="8"/>
+    <n v="107903"/>
+    <n v="78"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="125"/>
+    <s v="William"/>
+    <s v="Williams"/>
+    <s v="William Williams"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2018-07-24T00:00:00"/>
+    <n v="7"/>
+    <n v="62818"/>
+    <n v="93"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="126"/>
+    <s v="David"/>
+    <s v="Williams"/>
+    <s v="David Williams"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2018-07-20T00:00:00"/>
+    <n v="7"/>
+    <n v="85151"/>
+    <n v="68"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="127"/>
+    <s v="Jane"/>
+    <s v="Davis"/>
+    <s v="Jane Davis"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2016-03-04T00:00:00"/>
+    <n v="10"/>
+    <n v="46390"/>
+    <n v="42"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="128"/>
+    <s v="John"/>
+    <s v="Martinez"/>
+    <s v="John Martinez"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2022-03-23T00:00:00"/>
+    <n v="4"/>
+    <n v="111920"/>
+    <n v="34"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="129"/>
+    <s v="David"/>
+    <s v="Anderson"/>
+    <s v="David Anderson"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2017-07-28T00:00:00"/>
+    <n v="8"/>
+    <n v="115618"/>
+    <n v="35"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="130"/>
+    <s v="Sarah"/>
+    <s v="Smith"/>
+    <s v="Sarah Smith"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2023-11-05T00:00:00"/>
+    <n v="2"/>
+    <n v="110618"/>
+    <n v="95"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="131"/>
+    <s v="Melissa"/>
+    <s v="Hernandez"/>
+    <s v="Melissa Hernandez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2022-03-19T00:00:00"/>
+    <n v="4"/>
+    <n v="108395"/>
+    <n v="68.219858156028366"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="132"/>
+    <s v="Melissa"/>
+    <s v="Johnson"/>
+    <s v="Melissa Johnson"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2017-12-22T00:00:00"/>
+    <n v="8"/>
+    <n v="88005"/>
+    <n v="90"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="133"/>
+    <s v="Jane"/>
+    <s v="Garcia"/>
+    <s v="Jane Garcia"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2021-08-29T00:00:00"/>
+    <n v="4"/>
+    <n v="83007"/>
+    <n v="42"/>
+    <s v="Needs Improvement"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="134"/>
+    <s v="David"/>
+    <s v="Davis"/>
+    <s v="David Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2018-09-17T00:00:00"/>
+    <n v="7"/>
+    <n v="61547"/>
+    <n v="88"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="135"/>
+    <s v="James"/>
+    <s v="Wilson"/>
+    <s v="James Wilson"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2021-06-28T00:00:00"/>
+    <n v="5"/>
+    <n v="87282.34782608696"/>
+    <n v="78"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="136"/>
+    <s v="Richard"/>
+    <s v="Johnson"/>
+    <s v="Richard Johnson"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2017-10-03T00:00:00"/>
+    <n v="8"/>
+    <n v="50399"/>
+    <n v="69"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="137"/>
+    <s v="Richard"/>
+    <s v="Williams"/>
+    <s v="Richard Williams"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2015-10-22T00:00:00"/>
+    <n v="10"/>
+    <n v="87938.5"/>
+    <n v="66"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="138"/>
+    <s v="John"/>
+    <s v="Hernandez"/>
+    <s v="John Hernandez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2018-06-06T00:00:00"/>
+    <n v="8"/>
+    <n v="52720"/>
+    <n v="82"/>
+    <s v="Achieving"/>
+    <n v="0.05"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="139"/>
+    <s v="Sarah"/>
+    <s v="Gonzalez"/>
+    <s v="Sarah Gonzalez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2017-07-16T00:00:00"/>
+    <n v="8"/>
+    <n v="65065"/>
+    <n v="68"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="140"/>
+    <s v="Melissa"/>
+    <s v="Hernandez"/>
+    <s v="Melissa Hernandez"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2015-06-20T00:00:00"/>
+    <n v="11"/>
+    <n v="87282.34782608696"/>
+    <n v="52"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="141"/>
+    <s v="Melissa"/>
+    <s v="Hernandez"/>
+    <s v="Melissa Hernandez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2019-05-24T00:00:00"/>
+    <n v="7"/>
+    <n v="108119"/>
+    <n v="92"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="142"/>
+    <s v="John"/>
+    <s v="Davis"/>
+    <s v="John Davis"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2020-02-26T00:00:00"/>
+    <n v="6"/>
+    <n v="80014.258064516136"/>
+    <n v="62"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="143"/>
+    <s v="Richard"/>
+    <s v="Davis"/>
+    <s v="Richard Davis"/>
+    <x v="5"/>
+    <s v="HR01"/>
+    <d v="2023-03-06T00:00:00"/>
+    <n v="3"/>
+    <n v="106896"/>
+    <n v="68"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="144"/>
+    <s v="Unknown"/>
+    <s v="Jones"/>
+    <s v="Unknown Jones"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2019-12-01T00:00:00"/>
+    <n v="6"/>
+    <n v="112887"/>
+    <n v="98"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="145"/>
+    <s v="William"/>
+    <s v="Rodriguez"/>
+    <s v="William Rodriguez"/>
+    <x v="2"/>
+    <s v="FIN03"/>
+    <d v="2023-04-21T00:00:00"/>
+    <n v="3"/>
+    <n v="85457"/>
+    <n v="94"/>
+    <s v="Exceeding"/>
+    <n v="0.08"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="146"/>
+    <s v="Melissa"/>
+    <s v="Miller"/>
+    <s v="Melissa Miller"/>
+    <x v="4"/>
+    <s v="SAL05"/>
+    <d v="2016-05-29T00:00:00"/>
+    <n v="10"/>
+    <n v="62798"/>
+    <n v="57"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="147"/>
+    <s v="Emily"/>
+    <s v="Martinez"/>
+    <s v="Emily Martinez"/>
+    <x v="3"/>
+    <s v="OPS06"/>
+    <d v="2022-05-30T00:00:00"/>
+    <n v="4"/>
+    <n v="47794"/>
+    <n v="96"/>
+    <s v="Outstanding"/>
+    <n v="0.12"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="148"/>
+    <s v="James"/>
+    <s v="Rodriguez"/>
+    <s v="James Rodriguez"/>
+    <x v="1"/>
+    <s v="MKT04"/>
+    <d v="2016-11-03T00:00:00"/>
+    <n v="9"/>
+    <n v="93094"/>
+    <n v="52"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="149"/>
+    <s v="Amanda"/>
+    <s v="Brown"/>
+    <s v="Amanda Brown"/>
+    <x v="0"/>
+    <s v="IT02"/>
+    <d v="2022-10-14T00:00:00"/>
+    <n v="3"/>
+    <n v="118634"/>
+    <n v="59"/>
+    <s v="Developing"/>
+    <n v="0.02"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department_Name">
+  <location ref="F3:J11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0">
+      <items count="151">
+        <item x="66"/>
+        <item x="136"/>
+        <item x="121"/>
+        <item x="113"/>
+        <item x="56"/>
+        <item x="91"/>
+        <item x="118"/>
+        <item x="100"/>
+        <item x="109"/>
+        <item x="22"/>
+        <item x="63"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="110"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="61"/>
+        <item x="114"/>
+        <item x="20"/>
+        <item x="10"/>
+        <item x="145"/>
+        <item x="131"/>
+        <item x="45"/>
+        <item x="74"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item x="39"/>
+        <item x="52"/>
+        <item x="71"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="57"/>
+        <item x="84"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="43"/>
+        <item x="134"/>
+        <item x="115"/>
+        <item x="76"/>
+        <item x="72"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="101"/>
+        <item x="69"/>
+        <item x="1"/>
+        <item x="99"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="94"/>
+        <item x="127"/>
+        <item x="25"/>
+        <item x="137"/>
+        <item x="90"/>
+        <item x="125"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="132"/>
+        <item x="128"/>
+        <item x="111"/>
+        <item x="58"/>
+        <item x="82"/>
+        <item x="87"/>
+        <item x="123"/>
+        <item x="68"/>
+        <item x="18"/>
+        <item x="60"/>
+        <item x="37"/>
+        <item x="50"/>
+        <item x="13"/>
+        <item x="102"/>
+        <item x="146"/>
+        <item x="116"/>
+        <item x="83"/>
+        <item x="143"/>
+        <item x="30"/>
+        <item x="44"/>
+        <item x="97"/>
+        <item x="41"/>
+        <item x="49"/>
+        <item x="96"/>
+        <item x="24"/>
+        <item x="70"/>
+        <item x="105"/>
+        <item x="34"/>
+        <item x="77"/>
+        <item x="53"/>
+        <item x="142"/>
+        <item x="130"/>
+        <item x="108"/>
+        <item x="64"/>
+        <item x="104"/>
+        <item x="148"/>
+        <item x="88"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item x="28"/>
+        <item x="140"/>
+        <item x="120"/>
+        <item x="59"/>
+        <item x="149"/>
+        <item x="139"/>
+        <item x="85"/>
+        <item x="35"/>
+        <item x="147"/>
+        <item x="126"/>
+        <item x="17"/>
+        <item x="92"/>
+        <item x="75"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="81"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="141"/>
+        <item x="86"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="122"/>
+        <item x="144"/>
+        <item x="62"/>
+        <item x="78"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="26"/>
+        <item x="133"/>
+        <item x="138"/>
+        <item x="79"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="112"/>
+        <item x="40"/>
+        <item x="31"/>
+        <item x="117"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="47"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="119"/>
+        <item x="65"/>
+        <item x="27"/>
+        <item x="93"/>
+        <item x="135"/>
+        <item x="42"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="12"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department_Name">
+  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0">
+      <items count="151">
+        <item x="66"/>
+        <item x="136"/>
+        <item x="121"/>
+        <item x="113"/>
+        <item x="56"/>
+        <item x="91"/>
+        <item x="118"/>
+        <item x="100"/>
+        <item x="109"/>
+        <item x="22"/>
+        <item x="63"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="110"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="61"/>
+        <item x="114"/>
+        <item x="20"/>
+        <item x="10"/>
+        <item x="145"/>
+        <item x="131"/>
+        <item x="45"/>
+        <item x="74"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item x="39"/>
+        <item x="52"/>
+        <item x="71"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="57"/>
+        <item x="84"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="43"/>
+        <item x="134"/>
+        <item x="115"/>
+        <item x="76"/>
+        <item x="72"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="101"/>
+        <item x="69"/>
+        <item x="1"/>
+        <item x="99"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="94"/>
+        <item x="127"/>
+        <item x="25"/>
+        <item x="137"/>
+        <item x="90"/>
+        <item x="125"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="132"/>
+        <item x="128"/>
+        <item x="111"/>
+        <item x="58"/>
+        <item x="82"/>
+        <item x="87"/>
+        <item x="123"/>
+        <item x="68"/>
+        <item x="18"/>
+        <item x="60"/>
+        <item x="37"/>
+        <item x="50"/>
+        <item x="13"/>
+        <item x="102"/>
+        <item x="146"/>
+        <item x="116"/>
+        <item x="83"/>
+        <item x="143"/>
+        <item x="30"/>
+        <item x="44"/>
+        <item x="97"/>
+        <item x="41"/>
+        <item x="49"/>
+        <item x="96"/>
+        <item x="24"/>
+        <item x="70"/>
+        <item x="105"/>
+        <item x="34"/>
+        <item x="77"/>
+        <item x="53"/>
+        <item x="142"/>
+        <item x="130"/>
+        <item x="108"/>
+        <item x="64"/>
+        <item x="104"/>
+        <item x="148"/>
+        <item x="88"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item x="28"/>
+        <item x="140"/>
+        <item x="120"/>
+        <item x="59"/>
+        <item x="149"/>
+        <item x="139"/>
+        <item x="85"/>
+        <item x="35"/>
+        <item x="147"/>
+        <item x="126"/>
+        <item x="17"/>
+        <item x="92"/>
+        <item x="75"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="81"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="141"/>
+        <item x="86"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="122"/>
+        <item x="144"/>
+        <item x="62"/>
+        <item x="78"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="26"/>
+        <item x="133"/>
+        <item x="138"/>
+        <item x="79"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="112"/>
+        <item x="40"/>
+        <item x="31"/>
+        <item x="117"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="47"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="119"/>
+        <item x="65"/>
+        <item x="27"/>
+        <item x="93"/>
+        <item x="135"/>
+        <item x="42"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}" name="Table1" displayName="Table1" ref="J1:V151" totalsRowShown="0">
+  <autoFilter ref="J1:V151" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="12">
+      <calculatedColumnFormula>TRIM(CLEAN(A2))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="11">
+      <calculatedColumnFormula>TRIM(CLEAN(PROPER(B2)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="10">
+      <calculatedColumnFormula>TRIM(CLEAN(PROPER(C2)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="9">
+      <calculatedColumnFormula>_xlfn.TEXTJOIN(" ",TRUE,K2,L2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="8">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(O2,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="7">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(D2,Lookup_Departments!$A$2:$B$7,1,FALSE),"Invalid")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="6">
+      <calculatedColumnFormula>IF(ISNUMBER(E2),E2,DATE(RIGHT(E2,4),LEFT(E2,2),MID(E2,4,2)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="5">
+      <calculatedColumnFormula>DATEDIF(P2,TODAY(),"Y")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="4">
+      <calculatedColumnFormula>IF(F2="",AVERAGEIF($D$2:$D$151,D2,$F$2:$F$151),F2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="3">
+      <calculatedColumnFormula>IF(G2="",AVERAGE($G$2:$G$158),G2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="2">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Amount" dataDxfId="1">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="0">
+      <calculatedColumnFormula>TRIM(CLEAN(UPPER(H2)))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1279,6 +4389,246 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75D2B25-32D9-44F6-8017-10CE3B25D12A}">
+  <dimension ref="A2:L11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" style="29" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.35">
+      <c r="A2" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="20">
+        <v>17</v>
+      </c>
+      <c r="C4" s="20">
+        <v>87938.5</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="G4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I4" t="s">
+        <v>267</v>
+      </c>
+      <c r="J4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" s="20">
+        <v>18</v>
+      </c>
+      <c r="C5" s="20">
+        <v>85649.941176470587</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="20">
+        <v>13</v>
+      </c>
+      <c r="H5" s="20">
+        <v>2</v>
+      </c>
+      <c r="I5" s="20">
+        <v>2</v>
+      </c>
+      <c r="J5" s="20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="20">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20">
+        <v>80014.258064516151</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="20">
+        <v>16</v>
+      </c>
+      <c r="H6" s="20">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1</v>
+      </c>
+      <c r="J6" s="20">
+        <v>18</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="20">
+        <v>19</v>
+      </c>
+      <c r="C7" s="20">
+        <v>85508.166666666657</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G7" s="20">
+        <v>28</v>
+      </c>
+      <c r="H7" s="20">
+        <v>3</v>
+      </c>
+      <c r="I7" s="20">
+        <v>5</v>
+      </c>
+      <c r="J7" s="20">
+        <v>36</v>
+      </c>
+      <c r="L7" s="30">
+        <f>(GETPIVOTDATA("Cleaned EMP ID",$F$3,"Cleaned Employment_Status","LEFT")+GETPIVOTDATA("Cleaned EMP ID",$F$3,"Cleaned Employment_Status","RESIGNED"))/GETPIVOTDATA("Cleaned EMP ID",$F$3)</f>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="20">
+        <v>29</v>
+      </c>
+      <c r="C8" s="20">
+        <v>79786.666666666657</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="G8" s="20">
+        <v>16</v>
+      </c>
+      <c r="H8" s="20">
+        <v>3</v>
+      </c>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="20">
+        <v>31</v>
+      </c>
+      <c r="C9" s="20">
+        <v>87282.347826086945</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="20">
+        <v>22</v>
+      </c>
+      <c r="H9" s="20">
+        <v>7</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F10" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="G10" s="20">
+        <v>22</v>
+      </c>
+      <c r="H10" s="20">
+        <v>7</v>
+      </c>
+      <c r="I10" s="20">
+        <v>2</v>
+      </c>
+      <c r="J10" s="20">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F11" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="G11" s="20">
+        <v>117</v>
+      </c>
+      <c r="H11" s="20">
+        <v>23</v>
+      </c>
+      <c r="I11" s="20">
+        <v>10</v>
+      </c>
+      <c r="J11" s="20">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDFAF64-CC90-44C1-8412-C55F11F76DC5}">
   <dimension ref="A1:W158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1292,19 +4642,19 @@
     <col min="7" max="7" width="9.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.36328125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7265625" style="21" customWidth="1"/>
-    <col min="14" max="14" width="20.90625" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.81640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="19.54296875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="19.26953125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="17.7265625" style="22" customWidth="1"/>
+    <col min="14" max="14" width="20.90625" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.36328125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="16.08984375" style="17" customWidth="1"/>
+    <col min="18" max="18" width="15" style="14" customWidth="1"/>
+    <col min="19" max="19" width="19" style="17" customWidth="1"/>
+    <col min="20" max="20" width="18.90625" style="6" customWidth="1"/>
+    <col min="21" max="21" width="22.6328125" style="24" customWidth="1"/>
+    <col min="22" max="22" width="26.90625" style="6" customWidth="1"/>
     <col min="23" max="23" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1333,43 +4683,43 @@
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="M1" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="S1" s="16" t="s">
         <v>275</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>273</v>
       </c>
       <c r="T1" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="U1" s="22" t="s">
-        <v>277</v>
+      <c r="U1" s="23" t="s">
+        <v>279</v>
       </c>
       <c r="V1" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
@@ -1409,11 +4759,11 @@
         <f>TRIM(CLEAN(PROPER(C2)))</f>
         <v>Brown</v>
       </c>
-      <c r="M2" s="21" t="str">
+      <c r="M2" s="22" t="str">
         <f>_xlfn.TEXTJOIN(" ",TRUE,K2,L2)</f>
         <v>Emily Brown</v>
       </c>
-      <c r="N2" s="21" t="str">
+      <c r="N2" s="22" t="str">
         <f>_xlfn.XLOOKUP(O2,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -1441,7 +4791,7 @@
         <f>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U2" s="23">
+      <c r="U2" s="24">
         <f>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -1486,11 +4836,11 @@
         <f>TRIM(CLEAN(PROPER(C3)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M3" s="21" t="str">
+      <c r="M3" s="22" t="str">
         <f t="shared" ref="M3:M66" si="0">_xlfn.TEXTJOIN(" ",TRUE,K3,L3)</f>
         <v>Richard Hernandez</v>
       </c>
-      <c r="N3" s="21" t="str">
+      <c r="N3" s="22" t="str">
         <f>_xlfn.XLOOKUP(O3,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -1518,7 +4868,7 @@
         <f>_xlfn.XLOOKUP(S3,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U3" s="23">
+      <c r="U3" s="24">
         <f>_xlfn.XLOOKUP(S3,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -1564,11 +4914,11 @@
         <f>TRIM(CLEAN(PROPER(C4)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M4" s="21" t="str">
+      <c r="M4" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Gonzalez</v>
       </c>
-      <c r="N4" s="21" t="str">
+      <c r="N4" s="22" t="str">
         <f>_xlfn.XLOOKUP(O4,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -1596,7 +4946,7 @@
         <f>_xlfn.XLOOKUP(S4,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U4" s="23">
+      <c r="U4" s="24">
         <f>_xlfn.XLOOKUP(S4,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -1642,11 +4992,11 @@
         <f>TRIM(CLEAN(PROPER(C5)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M5" s="21" t="str">
+      <c r="M5" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Martinez</v>
       </c>
-      <c r="N5" s="21" t="str">
+      <c r="N5" s="22" t="str">
         <f>_xlfn.XLOOKUP(O5,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -1674,7 +5024,7 @@
         <f>_xlfn.XLOOKUP(S5,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U5" s="23">
+      <c r="U5" s="24">
         <f>_xlfn.XLOOKUP(S5,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -1720,11 +5070,11 @@
         <f>TRIM(CLEAN(PROPER(C6)))</f>
         <v>Smith</v>
       </c>
-      <c r="M6" s="21" t="str">
+      <c r="M6" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Smith</v>
       </c>
-      <c r="N6" s="21" t="str">
+      <c r="N6" s="22" t="str">
         <f>_xlfn.XLOOKUP(O6,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -1752,7 +5102,7 @@
         <f>_xlfn.XLOOKUP(S6,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="24">
         <f>_xlfn.XLOOKUP(S6,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -1798,11 +5148,11 @@
         <f>TRIM(CLEAN(PROPER(C7)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M7" s="21" t="str">
+      <c r="M7" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Johnson</v>
       </c>
-      <c r="N7" s="21" t="str">
+      <c r="N7" s="22" t="str">
         <f>_xlfn.XLOOKUP(O7,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -1830,7 +5180,7 @@
         <f>_xlfn.XLOOKUP(S7,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="24">
         <f>_xlfn.XLOOKUP(S7,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -1876,11 +5226,11 @@
         <f>TRIM(CLEAN(PROPER(C8)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M8" s="21" t="str">
+      <c r="M8" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Wilson</v>
       </c>
-      <c r="N8" s="21" t="str">
+      <c r="N8" s="22" t="str">
         <f>_xlfn.XLOOKUP(O8,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -1908,7 +5258,7 @@
         <f>_xlfn.XLOOKUP(S8,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="24">
         <f>_xlfn.XLOOKUP(S8,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -1954,11 +5304,11 @@
         <f>TRIM(CLEAN(PROPER(C9)))</f>
         <v>Smith</v>
       </c>
-      <c r="M9" s="21" t="str">
+      <c r="M9" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jessica Smith</v>
       </c>
-      <c r="N9" s="21" t="str">
+      <c r="N9" s="22" t="str">
         <f>_xlfn.XLOOKUP(O9,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -1986,7 +5336,7 @@
         <f>_xlfn.XLOOKUP(S9,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="24">
         <f>_xlfn.XLOOKUP(S9,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -2000,7 +5350,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>40</v>
@@ -2032,11 +5382,11 @@
         <f>TRIM(CLEAN(PROPER(C10)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M10" s="21" t="str">
+      <c r="M10" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Unknown Rodriguez</v>
       </c>
-      <c r="N10" s="21" t="str">
+      <c r="N10" s="22" t="str">
         <f>_xlfn.XLOOKUP(O10,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -2064,7 +5414,7 @@
         <f>_xlfn.XLOOKUP(S10,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="24">
         <f>_xlfn.XLOOKUP(S10,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -2110,11 +5460,11 @@
         <f>TRIM(CLEAN(PROPER(C11)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M11" s="21" t="str">
+      <c r="M11" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Martinez</v>
       </c>
-      <c r="N11" s="21" t="str">
+      <c r="N11" s="22" t="str">
         <f>_xlfn.XLOOKUP(O11,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -2142,7 +5492,7 @@
         <f>_xlfn.XLOOKUP(S11,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="24">
         <f>_xlfn.XLOOKUP(S11,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -2188,11 +5538,11 @@
         <f>TRIM(CLEAN(PROPER(C12)))</f>
         <v>Miller</v>
       </c>
-      <c r="M12" s="21" t="str">
+      <c r="M12" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Miller</v>
       </c>
-      <c r="N12" s="21" t="str">
+      <c r="N12" s="22" t="str">
         <f>_xlfn.XLOOKUP(O12,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -2220,7 +5570,7 @@
         <f>_xlfn.XLOOKUP(S12,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="24">
         <f>_xlfn.XLOOKUP(S12,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -2266,11 +5616,11 @@
         <f>TRIM(CLEAN(PROPER(C13)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M13" s="21" t="str">
+      <c r="M13" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Hernandez</v>
       </c>
-      <c r="N13" s="21" t="str">
+      <c r="N13" s="22" t="str">
         <f>_xlfn.XLOOKUP(O13,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -2298,7 +5648,7 @@
         <f>_xlfn.XLOOKUP(S13,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="24">
         <f>_xlfn.XLOOKUP(S13,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -2344,11 +5694,11 @@
         <f>TRIM(CLEAN(PROPER(C14)))</f>
         <v>Williams</v>
       </c>
-      <c r="M14" s="21" t="str">
+      <c r="M14" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Williams</v>
       </c>
-      <c r="N14" s="21" t="str">
+      <c r="N14" s="22" t="str">
         <f>_xlfn.XLOOKUP(O14,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -2376,7 +5726,7 @@
         <f>_xlfn.XLOOKUP(S14,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="24">
         <f>_xlfn.XLOOKUP(S14,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -2422,11 +5772,11 @@
         <f>TRIM(CLEAN(PROPER(C15)))</f>
         <v>Miller</v>
       </c>
-      <c r="M15" s="21" t="str">
+      <c r="M15" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Miller</v>
       </c>
-      <c r="N15" s="21" t="str">
+      <c r="N15" s="22" t="str">
         <f>_xlfn.XLOOKUP(O15,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -2454,7 +5804,7 @@
         <f>_xlfn.XLOOKUP(S15,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="24">
         <f>_xlfn.XLOOKUP(S15,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -2498,11 +5848,11 @@
         <f>TRIM(CLEAN(PROPER(C16)))</f>
         <v>Jones</v>
       </c>
-      <c r="M16" s="21" t="str">
+      <c r="M16" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Robert Jones</v>
       </c>
-      <c r="N16" s="21" t="str">
+      <c r="N16" s="22" t="str">
         <f>_xlfn.XLOOKUP(O16,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -2530,7 +5880,7 @@
         <f>_xlfn.XLOOKUP(S16,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U16" s="23">
+      <c r="U16" s="24">
         <f>_xlfn.XLOOKUP(S16,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -2576,11 +5926,11 @@
         <f>TRIM(CLEAN(PROPER(C17)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M17" s="21" t="str">
+      <c r="M17" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Rodriguez</v>
       </c>
-      <c r="N17" s="21" t="str">
+      <c r="N17" s="22" t="str">
         <f>_xlfn.XLOOKUP(O17,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -2608,7 +5958,7 @@
         <f>_xlfn.XLOOKUP(S17,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U17" s="23">
+      <c r="U17" s="24">
         <f>_xlfn.XLOOKUP(S17,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -2654,11 +6004,11 @@
         <f>TRIM(CLEAN(PROPER(C18)))</f>
         <v>Davis</v>
       </c>
-      <c r="M18" s="21" t="str">
+      <c r="M18" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Davis</v>
       </c>
-      <c r="N18" s="21" t="str">
+      <c r="N18" s="22" t="str">
         <f>_xlfn.XLOOKUP(O18,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -2686,7 +6036,7 @@
         <f>_xlfn.XLOOKUP(S18,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U18" s="23">
+      <c r="U18" s="24">
         <f>_xlfn.XLOOKUP(S18,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -2732,11 +6082,11 @@
         <f>TRIM(CLEAN(PROPER(C19)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M19" s="21" t="str">
+      <c r="M19" s="22" t="str">
         <f t="shared" si="0"/>
         <v>James Martinez</v>
       </c>
-      <c r="N19" s="21" t="str">
+      <c r="N19" s="22" t="str">
         <f>_xlfn.XLOOKUP(O19,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -2764,7 +6114,7 @@
         <f>_xlfn.XLOOKUP(S19,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U19" s="23">
+      <c r="U19" s="24">
         <f>_xlfn.XLOOKUP(S19,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -2810,11 +6160,11 @@
         <f>TRIM(CLEAN(PROPER(C20)))</f>
         <v>Lopez</v>
       </c>
-      <c r="M20" s="21" t="str">
+      <c r="M20" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Ashley Lopez</v>
       </c>
-      <c r="N20" s="21" t="str">
+      <c r="N20" s="22" t="str">
         <f>_xlfn.XLOOKUP(O20,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -2842,7 +6192,7 @@
         <f>_xlfn.XLOOKUP(S20,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U20" s="23">
+      <c r="U20" s="24">
         <f>_xlfn.XLOOKUP(S20,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -2885,11 +6235,11 @@
         <f>TRIM(CLEAN(PROPER(C21)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M21" s="21" t="str">
+      <c r="M21" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Amanda Gonzalez</v>
       </c>
-      <c r="N21" s="21" t="str">
+      <c r="N21" s="22" t="str">
         <f>_xlfn.XLOOKUP(O21,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -2917,7 +6267,7 @@
         <f>_xlfn.XLOOKUP(S21,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U21" s="23">
+      <c r="U21" s="24">
         <f>_xlfn.XLOOKUP(S21,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -2963,11 +6313,11 @@
         <f>TRIM(CLEAN(PROPER(C22)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M22" s="21" t="str">
+      <c r="M22" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Hernandez</v>
       </c>
-      <c r="N22" s="21" t="str">
+      <c r="N22" s="22" t="str">
         <f>_xlfn.XLOOKUP(O22,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -2995,7 +6345,7 @@
         <f>_xlfn.XLOOKUP(S22,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U22" s="23">
+      <c r="U22" s="24">
         <f>_xlfn.XLOOKUP(S22,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -3041,11 +6391,11 @@
         <f>TRIM(CLEAN(PROPER(C23)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M23" s="21" t="str">
+      <c r="M23" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Richard Hernandez</v>
       </c>
-      <c r="N23" s="21" t="str">
+      <c r="N23" s="22" t="str">
         <f>_xlfn.XLOOKUP(O23,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -3073,7 +6423,7 @@
         <f>_xlfn.XLOOKUP(S23,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U23" s="23">
+      <c r="U23" s="24">
         <f>_xlfn.XLOOKUP(S23,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3119,11 +6469,11 @@
         <f>TRIM(CLEAN(PROPER(C24)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M24" s="21" t="str">
+      <c r="M24" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Rodriguez</v>
       </c>
-      <c r="N24" s="21" t="str">
+      <c r="N24" s="22" t="str">
         <f>_xlfn.XLOOKUP(O24,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -3151,7 +6501,7 @@
         <f>_xlfn.XLOOKUP(S24,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U24" s="23">
+      <c r="U24" s="24">
         <f>_xlfn.XLOOKUP(S24,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -3197,11 +6547,11 @@
         <f>TRIM(CLEAN(PROPER(C25)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M25" s="21" t="str">
+      <c r="M25" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jessica Johnson</v>
       </c>
-      <c r="N25" s="21" t="str">
+      <c r="N25" s="22" t="str">
         <f>_xlfn.XLOOKUP(O25,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -3229,7 +6579,7 @@
         <f>_xlfn.XLOOKUP(S25,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U25" s="23">
+      <c r="U25" s="24">
         <f>_xlfn.XLOOKUP(S25,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3275,11 +6625,11 @@
         <f>TRIM(CLEAN(PROPER(C26)))</f>
         <v>Williams</v>
       </c>
-      <c r="M26" s="21" t="str">
+      <c r="M26" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Ashley Williams</v>
       </c>
-      <c r="N26" s="21" t="str">
+      <c r="N26" s="22" t="str">
         <f>_xlfn.XLOOKUP(O26,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -3307,7 +6657,7 @@
         <f>_xlfn.XLOOKUP(S26,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U26" s="23">
+      <c r="U26" s="24">
         <f>_xlfn.XLOOKUP(S26,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3321,7 +6671,7 @@
         <v>76</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>53</v>
@@ -3353,11 +6703,11 @@
         <f>TRIM(CLEAN(PROPER(C27)))</f>
         <v>Williams</v>
       </c>
-      <c r="M27" s="21" t="str">
+      <c r="M27" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Unknown Williams</v>
       </c>
-      <c r="N27" s="21" t="str">
+      <c r="N27" s="22" t="str">
         <f>_xlfn.XLOOKUP(O27,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -3385,7 +6735,7 @@
         <f>_xlfn.XLOOKUP(S27,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U27" s="23">
+      <c r="U27" s="24">
         <f>_xlfn.XLOOKUP(S27,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -3431,11 +6781,11 @@
         <f>TRIM(CLEAN(PROPER(C28)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M28" s="21" t="str">
+      <c r="M28" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Wilson</v>
       </c>
-      <c r="N28" s="21" t="str">
+      <c r="N28" s="22" t="str">
         <f>_xlfn.XLOOKUP(O28,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -3463,7 +6813,7 @@
         <f>_xlfn.XLOOKUP(S28,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U28" s="23">
+      <c r="U28" s="24">
         <f>_xlfn.XLOOKUP(S28,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3509,11 +6859,11 @@
         <f>TRIM(CLEAN(PROPER(C29)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M29" s="21" t="str">
+      <c r="M29" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Rodriguez</v>
       </c>
-      <c r="N29" s="21" t="str">
+      <c r="N29" s="22" t="str">
         <f>_xlfn.XLOOKUP(O29,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -3541,7 +6891,7 @@
         <f>_xlfn.XLOOKUP(S29,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U29" s="23">
+      <c r="U29" s="24">
         <f>_xlfn.XLOOKUP(S29,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -3587,11 +6937,11 @@
         <f>TRIM(CLEAN(PROPER(C30)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M30" s="21" t="str">
+      <c r="M30" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Wilson</v>
       </c>
-      <c r="N30" s="21" t="str">
+      <c r="N30" s="22" t="str">
         <f>_xlfn.XLOOKUP(O30,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -3619,7 +6969,7 @@
         <f>_xlfn.XLOOKUP(S30,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U30" s="23">
+      <c r="U30" s="24">
         <f>_xlfn.XLOOKUP(S30,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -3662,11 +7012,11 @@
         <f>TRIM(CLEAN(PROPER(C31)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M31" s="21" t="str">
+      <c r="M31" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Rodriguez</v>
       </c>
-      <c r="N31" s="21" t="str">
+      <c r="N31" s="22" t="str">
         <f>_xlfn.XLOOKUP(O31,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -3694,7 +7044,7 @@
         <f>_xlfn.XLOOKUP(S31,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U31" s="23">
+      <c r="U31" s="24">
         <f>_xlfn.XLOOKUP(S31,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3740,11 +7090,11 @@
         <f>TRIM(CLEAN(PROPER(C32)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M32" s="21" t="str">
+      <c r="M32" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Hernandez</v>
       </c>
-      <c r="N32" s="21" t="str">
+      <c r="N32" s="22" t="str">
         <f>_xlfn.XLOOKUP(O32,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -3772,7 +7122,7 @@
         <f>_xlfn.XLOOKUP(S32,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U32" s="23">
+      <c r="U32" s="24">
         <f>_xlfn.XLOOKUP(S32,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -3818,11 +7168,11 @@
         <f>TRIM(CLEAN(PROPER(C33)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M33" s="21" t="str">
+      <c r="M33" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Johnson</v>
       </c>
-      <c r="N33" s="21" t="str">
+      <c r="N33" s="22" t="str">
         <f>_xlfn.XLOOKUP(O33,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -3850,7 +7200,7 @@
         <f>_xlfn.XLOOKUP(S33,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U33" s="23">
+      <c r="U33" s="24">
         <f>_xlfn.XLOOKUP(S33,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -3896,11 +7246,11 @@
         <f>TRIM(CLEAN(PROPER(C34)))</f>
         <v>Brown</v>
       </c>
-      <c r="M34" s="21" t="str">
+      <c r="M34" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Sarah Brown</v>
       </c>
-      <c r="N34" s="21" t="str">
+      <c r="N34" s="22" t="str">
         <f>_xlfn.XLOOKUP(O34,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -3928,7 +7278,7 @@
         <f>_xlfn.XLOOKUP(S34,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U34" s="23">
+      <c r="U34" s="24">
         <f>_xlfn.XLOOKUP(S34,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -3974,11 +7324,11 @@
         <f>TRIM(CLEAN(PROPER(C35)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M35" s="21" t="str">
+      <c r="M35" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Martinez</v>
       </c>
-      <c r="N35" s="21" t="str">
+      <c r="N35" s="22" t="str">
         <f>_xlfn.XLOOKUP(O35,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -4006,7 +7356,7 @@
         <f>_xlfn.XLOOKUP(S35,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U35" s="23">
+      <c r="U35" s="24">
         <f>_xlfn.XLOOKUP(S35,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -4052,11 +7402,11 @@
         <f>TRIM(CLEAN(PROPER(C36)))</f>
         <v>Jones</v>
       </c>
-      <c r="M36" s="21" t="str">
+      <c r="M36" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Jones</v>
       </c>
-      <c r="N36" s="21" t="str">
+      <c r="N36" s="22" t="str">
         <f>_xlfn.XLOOKUP(O36,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -4084,7 +7434,7 @@
         <f>_xlfn.XLOOKUP(S36,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U36" s="23">
+      <c r="U36" s="24">
         <f>_xlfn.XLOOKUP(S36,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -4098,7 +7448,7 @@
         <v>94</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>10</v>
@@ -4130,11 +7480,11 @@
         <f>TRIM(CLEAN(PROPER(C37)))</f>
         <v>Brown</v>
       </c>
-      <c r="M37" s="21" t="str">
+      <c r="M37" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Unknown Brown</v>
       </c>
-      <c r="N37" s="21" t="str">
+      <c r="N37" s="22" t="str">
         <f>_xlfn.XLOOKUP(O37,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -4162,7 +7512,7 @@
         <f>_xlfn.XLOOKUP(S37,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U37" s="23">
+      <c r="U37" s="24">
         <f>_xlfn.XLOOKUP(S37,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -4208,11 +7558,11 @@
         <f>TRIM(CLEAN(PROPER(C38)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M38" s="21" t="str">
+      <c r="M38" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Wilson</v>
       </c>
-      <c r="N38" s="21" t="str">
+      <c r="N38" s="22" t="str">
         <f>_xlfn.XLOOKUP(O38,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -4240,7 +7590,7 @@
         <f>_xlfn.XLOOKUP(S38,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U38" s="23">
+      <c r="U38" s="24">
         <f>_xlfn.XLOOKUP(S38,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -4286,11 +7636,11 @@
         <f>TRIM(CLEAN(PROPER(C39)))</f>
         <v>Brown</v>
       </c>
-      <c r="M39" s="21" t="str">
+      <c r="M39" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Melissa Brown</v>
       </c>
-      <c r="N39" s="21" t="str">
+      <c r="N39" s="22" t="str">
         <f>_xlfn.XLOOKUP(O39,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -4318,7 +7668,7 @@
         <f>_xlfn.XLOOKUP(S39,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U39" s="23">
+      <c r="U39" s="24">
         <f>_xlfn.XLOOKUP(S39,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -4361,11 +7711,11 @@
         <f>TRIM(CLEAN(PROPER(C40)))</f>
         <v>Smith</v>
       </c>
-      <c r="M40" s="21" t="str">
+      <c r="M40" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Smith</v>
       </c>
-      <c r="N40" s="21" t="str">
+      <c r="N40" s="22" t="str">
         <f>_xlfn.XLOOKUP(O40,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -4393,7 +7743,7 @@
         <f>_xlfn.XLOOKUP(S40,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U40" s="23">
+      <c r="U40" s="24">
         <f>_xlfn.XLOOKUP(S40,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -4439,11 +7789,11 @@
         <f>TRIM(CLEAN(PROPER(C41)))</f>
         <v>Miller</v>
       </c>
-      <c r="M41" s="21" t="str">
+      <c r="M41" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Sarah Miller</v>
       </c>
-      <c r="N41" s="21" t="str">
+      <c r="N41" s="22" t="str">
         <f>_xlfn.XLOOKUP(O41,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -4471,7 +7821,7 @@
         <f>_xlfn.XLOOKUP(S41,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U41" s="23">
+      <c r="U41" s="24">
         <f>_xlfn.XLOOKUP(S41,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -4515,11 +7865,11 @@
         <f>TRIM(CLEAN(PROPER(C42)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M42" s="21" t="str">
+      <c r="M42" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Wilson</v>
       </c>
-      <c r="N42" s="21" t="str">
+      <c r="N42" s="22" t="str">
         <f>_xlfn.XLOOKUP(O42,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -4547,7 +7897,7 @@
         <f>_xlfn.XLOOKUP(S42,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U42" s="23">
+      <c r="U42" s="24">
         <f>_xlfn.XLOOKUP(S42,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -4593,11 +7943,11 @@
         <f>TRIM(CLEAN(PROPER(C43)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M43" s="21" t="str">
+      <c r="M43" s="22" t="str">
         <f t="shared" si="0"/>
         <v>David Hernandez</v>
       </c>
-      <c r="N43" s="21" t="str">
+      <c r="N43" s="22" t="str">
         <f>_xlfn.XLOOKUP(O43,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -4625,7 +7975,7 @@
         <f>_xlfn.XLOOKUP(S43,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U43" s="23">
+      <c r="U43" s="24">
         <f>_xlfn.XLOOKUP(S43,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -4671,11 +8021,11 @@
         <f>TRIM(CLEAN(PROPER(C44)))</f>
         <v>Smith</v>
       </c>
-      <c r="M44" s="21" t="str">
+      <c r="M44" s="22" t="str">
         <f t="shared" si="0"/>
         <v>James Smith</v>
       </c>
-      <c r="N44" s="21" t="str">
+      <c r="N44" s="22" t="str">
         <f>_xlfn.XLOOKUP(O44,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -4703,7 +8053,7 @@
         <f>_xlfn.XLOOKUP(S44,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U44" s="23">
+      <c r="U44" s="24">
         <f>_xlfn.XLOOKUP(S44,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -4749,11 +8099,11 @@
         <f>TRIM(CLEAN(PROPER(C45)))</f>
         <v>Williams</v>
       </c>
-      <c r="M45" s="21" t="str">
+      <c r="M45" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Sarah Williams</v>
       </c>
-      <c r="N45" s="21" t="str">
+      <c r="N45" s="22" t="str">
         <f>_xlfn.XLOOKUP(O45,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -4781,7 +8131,7 @@
         <f>_xlfn.XLOOKUP(S45,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U45" s="23">
+      <c r="U45" s="24">
         <f>_xlfn.XLOOKUP(S45,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -4827,11 +8177,11 @@
         <f>TRIM(CLEAN(PROPER(C46)))</f>
         <v>Lopez</v>
       </c>
-      <c r="M46" s="21" t="str">
+      <c r="M46" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Amanda Lopez</v>
       </c>
-      <c r="N46" s="21" t="str">
+      <c r="N46" s="22" t="str">
         <f>_xlfn.XLOOKUP(O46,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -4859,7 +8209,7 @@
         <f>_xlfn.XLOOKUP(S46,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U46" s="23">
+      <c r="U46" s="24">
         <f>_xlfn.XLOOKUP(S46,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -4905,11 +8255,11 @@
         <f>TRIM(CLEAN(PROPER(C47)))</f>
         <v>Lopez</v>
       </c>
-      <c r="M47" s="21" t="str">
+      <c r="M47" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Lopez</v>
       </c>
-      <c r="N47" s="21" t="str">
+      <c r="N47" s="22" t="str">
         <f>_xlfn.XLOOKUP(O47,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -4937,7 +8287,7 @@
         <f>_xlfn.XLOOKUP(S47,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U47" s="23">
+      <c r="U47" s="24">
         <f>_xlfn.XLOOKUP(S47,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -4983,11 +8333,11 @@
         <f>TRIM(CLEAN(PROPER(C48)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M48" s="21" t="str">
+      <c r="M48" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Melissa Johnson</v>
       </c>
-      <c r="N48" s="21" t="str">
+      <c r="N48" s="22" t="str">
         <f>_xlfn.XLOOKUP(O48,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -5015,7 +8365,7 @@
         <f>_xlfn.XLOOKUP(S48,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U48" s="23">
+      <c r="U48" s="24">
         <f>_xlfn.XLOOKUP(S48,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -5061,11 +8411,11 @@
         <f>TRIM(CLEAN(PROPER(C49)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M49" s="21" t="str">
+      <c r="M49" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Amanda Johnson</v>
       </c>
-      <c r="N49" s="21" t="str">
+      <c r="N49" s="22" t="str">
         <f>_xlfn.XLOOKUP(O49,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -5093,7 +8443,7 @@
         <f>_xlfn.XLOOKUP(S49,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U49" s="23">
+      <c r="U49" s="24">
         <f>_xlfn.XLOOKUP(S49,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -5139,11 +8489,11 @@
         <f>TRIM(CLEAN(PROPER(C50)))</f>
         <v>Davis</v>
       </c>
-      <c r="M50" s="21" t="str">
+      <c r="M50" s="22" t="str">
         <f t="shared" si="0"/>
         <v>John Davis</v>
       </c>
-      <c r="N50" s="21" t="str">
+      <c r="N50" s="22" t="str">
         <f>_xlfn.XLOOKUP(O50,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -5171,7 +8521,7 @@
         <f>_xlfn.XLOOKUP(S50,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U50" s="23">
+      <c r="U50" s="24">
         <f>_xlfn.XLOOKUP(S50,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -5217,11 +8567,11 @@
         <f>TRIM(CLEAN(PROPER(C51)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M51" s="21" t="str">
+      <c r="M51" s="22" t="str">
         <f t="shared" si="0"/>
         <v>James Johnson</v>
       </c>
-      <c r="N51" s="21" t="str">
+      <c r="N51" s="22" t="str">
         <f>_xlfn.XLOOKUP(O51,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -5249,7 +8599,7 @@
         <f>_xlfn.XLOOKUP(S51,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U51" s="23">
+      <c r="U51" s="24">
         <f>_xlfn.XLOOKUP(S51,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -5293,11 +8643,11 @@
         <f>TRIM(CLEAN(PROPER(C52)))</f>
         <v>Davis</v>
       </c>
-      <c r="M52" s="21" t="str">
+      <c r="M52" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Davis</v>
       </c>
-      <c r="N52" s="21" t="str">
+      <c r="N52" s="22" t="str">
         <f>_xlfn.XLOOKUP(O52,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -5325,7 +8675,7 @@
         <f>_xlfn.XLOOKUP(S52,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U52" s="23">
+      <c r="U52" s="24">
         <f>_xlfn.XLOOKUP(S52,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -5371,11 +8721,11 @@
         <f>TRIM(CLEAN(PROPER(C53)))</f>
         <v>Davis</v>
       </c>
-      <c r="M53" s="21" t="str">
+      <c r="M53" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Richard Davis</v>
       </c>
-      <c r="N53" s="21" t="str">
+      <c r="N53" s="22" t="str">
         <f>_xlfn.XLOOKUP(O53,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -5403,7 +8753,7 @@
         <f>_xlfn.XLOOKUP(S53,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U53" s="23">
+      <c r="U53" s="24">
         <f>_xlfn.XLOOKUP(S53,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -5449,11 +8799,11 @@
         <f>TRIM(CLEAN(PROPER(C54)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M54" s="21" t="str">
+      <c r="M54" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Rodriguez</v>
       </c>
-      <c r="N54" s="21" t="str">
+      <c r="N54" s="22" t="str">
         <f>_xlfn.XLOOKUP(O54,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -5481,7 +8831,7 @@
         <f>_xlfn.XLOOKUP(S54,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U54" s="23">
+      <c r="U54" s="24">
         <f>_xlfn.XLOOKUP(S54,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -5527,11 +8877,11 @@
         <f>TRIM(CLEAN(PROPER(C55)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M55" s="21" t="str">
+      <c r="M55" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Johnson</v>
       </c>
-      <c r="N55" s="21" t="str">
+      <c r="N55" s="22" t="str">
         <f>_xlfn.XLOOKUP(O55,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -5559,7 +8909,7 @@
         <f>_xlfn.XLOOKUP(S55,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U55" s="23">
+      <c r="U55" s="24">
         <f>_xlfn.XLOOKUP(S55,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -5605,11 +8955,11 @@
         <f>TRIM(CLEAN(PROPER(C56)))</f>
         <v>Garcia</v>
       </c>
-      <c r="M56" s="21" t="str">
+      <c r="M56" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Garcia</v>
       </c>
-      <c r="N56" s="21" t="str">
+      <c r="N56" s="22" t="str">
         <f>_xlfn.XLOOKUP(O56,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -5637,7 +8987,7 @@
         <f>_xlfn.XLOOKUP(S56,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U56" s="23">
+      <c r="U56" s="24">
         <f>_xlfn.XLOOKUP(S56,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -5680,11 +9030,11 @@
         <f>TRIM(CLEAN(PROPER(C57)))</f>
         <v>Anderson</v>
       </c>
-      <c r="M57" s="21" t="str">
+      <c r="M57" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Anderson</v>
       </c>
-      <c r="N57" s="21" t="str">
+      <c r="N57" s="22" t="str">
         <f>_xlfn.XLOOKUP(O57,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -5712,7 +9062,7 @@
         <f>_xlfn.XLOOKUP(S57,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U57" s="23">
+      <c r="U57" s="24">
         <f>_xlfn.XLOOKUP(S57,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -5755,11 +9105,11 @@
         <f>TRIM(CLEAN(PROPER(C58)))</f>
         <v>Garcia</v>
       </c>
-      <c r="M58" s="21" t="str">
+      <c r="M58" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Garcia</v>
       </c>
-      <c r="N58" s="21" t="str">
+      <c r="N58" s="22" t="str">
         <f>_xlfn.XLOOKUP(O58,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -5787,7 +9137,7 @@
         <f>_xlfn.XLOOKUP(S58,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U58" s="23">
+      <c r="U58" s="24">
         <f>_xlfn.XLOOKUP(S58,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -5833,11 +9183,11 @@
         <f>TRIM(CLEAN(PROPER(C59)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M59" s="21" t="str">
+      <c r="M59" s="22" t="str">
         <f t="shared" si="0"/>
         <v>David Martinez</v>
       </c>
-      <c r="N59" s="21" t="str">
+      <c r="N59" s="22" t="str">
         <f>_xlfn.XLOOKUP(O59,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -5865,7 +9215,7 @@
         <f>_xlfn.XLOOKUP(S59,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U59" s="23">
+      <c r="U59" s="24">
         <f>_xlfn.XLOOKUP(S59,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -5911,11 +9261,11 @@
         <f>TRIM(CLEAN(PROPER(C60)))</f>
         <v>Brown</v>
       </c>
-      <c r="M60" s="21" t="str">
+      <c r="M60" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Brown</v>
       </c>
-      <c r="N60" s="21" t="str">
+      <c r="N60" s="22" t="str">
         <f>_xlfn.XLOOKUP(O60,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -5943,7 +9293,7 @@
         <f>_xlfn.XLOOKUP(S60,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U60" s="23">
+      <c r="U60" s="24">
         <f>_xlfn.XLOOKUP(S60,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -5987,11 +9337,11 @@
         <f>TRIM(CLEAN(PROPER(C61)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M61" s="21" t="str">
+      <c r="M61" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Emily Wilson</v>
       </c>
-      <c r="N61" s="21" t="str">
+      <c r="N61" s="22" t="str">
         <f>_xlfn.XLOOKUP(O61,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -6019,7 +9369,7 @@
         <f>_xlfn.XLOOKUP(S61,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U61" s="23">
+      <c r="U61" s="24">
         <f>_xlfn.XLOOKUP(S61,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -6065,11 +9415,11 @@
         <f>TRIM(CLEAN(PROPER(C62)))</f>
         <v>Anderson</v>
       </c>
-      <c r="M62" s="21" t="str">
+      <c r="M62" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Michael Anderson</v>
       </c>
-      <c r="N62" s="21" t="str">
+      <c r="N62" s="22" t="str">
         <f>_xlfn.XLOOKUP(O62,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -6097,7 +9447,7 @@
         <f>_xlfn.XLOOKUP(S62,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U62" s="23">
+      <c r="U62" s="24">
         <f>_xlfn.XLOOKUP(S62,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -6143,11 +9493,11 @@
         <f>TRIM(CLEAN(PROPER(C63)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M63" s="21" t="str">
+      <c r="M63" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Robert Johnson</v>
       </c>
-      <c r="N63" s="21" t="str">
+      <c r="N63" s="22" t="str">
         <f>_xlfn.XLOOKUP(O63,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -6175,7 +9525,7 @@
         <f>_xlfn.XLOOKUP(S63,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U63" s="23">
+      <c r="U63" s="24">
         <f>_xlfn.XLOOKUP(S63,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -6221,11 +9571,11 @@
         <f>TRIM(CLEAN(PROPER(C64)))</f>
         <v>Miller</v>
       </c>
-      <c r="M64" s="21" t="str">
+      <c r="M64" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Robert Miller</v>
       </c>
-      <c r="N64" s="21" t="str">
+      <c r="N64" s="22" t="str">
         <f>_xlfn.XLOOKUP(O64,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -6253,7 +9603,7 @@
         <f>_xlfn.XLOOKUP(S64,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U64" s="23">
+      <c r="U64" s="24">
         <f>_xlfn.XLOOKUP(S64,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -6299,11 +9649,11 @@
         <f>TRIM(CLEAN(PROPER(C65)))</f>
         <v>Davis</v>
       </c>
-      <c r="M65" s="21" t="str">
+      <c r="M65" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Jane Davis</v>
       </c>
-      <c r="N65" s="21" t="str">
+      <c r="N65" s="22" t="str">
         <f>_xlfn.XLOOKUP(O65,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -6331,7 +9681,7 @@
         <f>_xlfn.XLOOKUP(S65,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U65" s="23">
+      <c r="U65" s="24">
         <f>_xlfn.XLOOKUP(S65,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -6374,11 +9724,11 @@
         <f>TRIM(CLEAN(PROPER(C66)))</f>
         <v>Davis</v>
       </c>
-      <c r="M66" s="21" t="str">
+      <c r="M66" s="22" t="str">
         <f t="shared" si="0"/>
         <v>Thomas Davis</v>
       </c>
-      <c r="N66" s="21" t="str">
+      <c r="N66" s="22" t="str">
         <f>_xlfn.XLOOKUP(O66,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -6406,7 +9756,7 @@
         <f>_xlfn.XLOOKUP(S66,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U66" s="23">
+      <c r="U66" s="24">
         <f>_xlfn.XLOOKUP(S66,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -6452,11 +9802,11 @@
         <f>TRIM(CLEAN(PROPER(C67)))</f>
         <v>Jones</v>
       </c>
-      <c r="M67" s="21" t="str">
+      <c r="M67" s="22" t="str">
         <f t="shared" ref="M67:M130" si="3">_xlfn.TEXTJOIN(" ",TRUE,K67,L67)</f>
         <v>Thomas Jones</v>
       </c>
-      <c r="N67" s="21" t="str">
+      <c r="N67" s="22" t="str">
         <f>_xlfn.XLOOKUP(O67,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -6484,7 +9834,7 @@
         <f>_xlfn.XLOOKUP(S67,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U67" s="23">
+      <c r="U67" s="24">
         <f>_xlfn.XLOOKUP(S67,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -6530,11 +9880,11 @@
         <f>TRIM(CLEAN(PROPER(C68)))</f>
         <v>Miller</v>
       </c>
-      <c r="M68" s="21" t="str">
+      <c r="M68" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Michael Miller</v>
       </c>
-      <c r="N68" s="21" t="str">
+      <c r="N68" s="22" t="str">
         <f>_xlfn.XLOOKUP(O68,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -6562,7 +9912,7 @@
         <f>_xlfn.XLOOKUP(S68,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U68" s="23">
+      <c r="U68" s="24">
         <f>_xlfn.XLOOKUP(S68,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -6606,11 +9956,11 @@
         <f>TRIM(CLEAN(PROPER(C69)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M69" s="21" t="str">
+      <c r="M69" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Richard Gonzalez</v>
       </c>
-      <c r="N69" s="21" t="str">
+      <c r="N69" s="22" t="str">
         <f>_xlfn.XLOOKUP(O69,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -6638,7 +9988,7 @@
         <f>_xlfn.XLOOKUP(S69,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U69" s="23">
+      <c r="U69" s="24">
         <f>_xlfn.XLOOKUP(S69,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -6681,11 +10031,11 @@
         <f>TRIM(CLEAN(PROPER(C70)))</f>
         <v>Williams</v>
       </c>
-      <c r="M70" s="21" t="str">
+      <c r="M70" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Williams</v>
       </c>
-      <c r="N70" s="21" t="str">
+      <c r="N70" s="22" t="str">
         <f>_xlfn.XLOOKUP(O70,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -6713,7 +10063,7 @@
         <f>_xlfn.XLOOKUP(S70,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U70" s="23">
+      <c r="U70" s="24">
         <f>_xlfn.XLOOKUP(S70,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -6759,11 +10109,11 @@
         <f>TRIM(CLEAN(PROPER(C71)))</f>
         <v>Miller</v>
       </c>
-      <c r="M71" s="21" t="str">
+      <c r="M71" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Robert Miller</v>
       </c>
-      <c r="N71" s="21" t="str">
+      <c r="N71" s="22" t="str">
         <f>_xlfn.XLOOKUP(O71,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -6791,7 +10141,7 @@
         <f>_xlfn.XLOOKUP(S71,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U71" s="23">
+      <c r="U71" s="24">
         <f>_xlfn.XLOOKUP(S71,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -6837,11 +10187,11 @@
         <f>TRIM(CLEAN(PROPER(C72)))</f>
         <v>Garcia</v>
       </c>
-      <c r="M72" s="21" t="str">
+      <c r="M72" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Garcia</v>
       </c>
-      <c r="N72" s="21" t="str">
+      <c r="N72" s="22" t="str">
         <f>_xlfn.XLOOKUP(O72,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -6869,7 +10219,7 @@
         <f>_xlfn.XLOOKUP(S72,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U72" s="23">
+      <c r="U72" s="24">
         <f>_xlfn.XLOOKUP(S72,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -6912,11 +10262,11 @@
         <f>TRIM(CLEAN(PROPER(C73)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M73" s="21" t="str">
+      <c r="M73" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Gonzalez</v>
       </c>
-      <c r="N73" s="21" t="str">
+      <c r="N73" s="22" t="str">
         <f>_xlfn.XLOOKUP(O73,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -6944,7 +10294,7 @@
         <f>_xlfn.XLOOKUP(S73,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U73" s="23">
+      <c r="U73" s="24">
         <f>_xlfn.XLOOKUP(S73,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -6987,11 +10337,11 @@
         <f>TRIM(CLEAN(PROPER(C74)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M74" s="21" t="str">
+      <c r="M74" s="22" t="str">
         <f t="shared" si="3"/>
         <v>James Gonzalez</v>
       </c>
-      <c r="N74" s="21" t="str">
+      <c r="N74" s="22" t="str">
         <f>_xlfn.XLOOKUP(O74,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -7019,7 +10369,7 @@
         <f>_xlfn.XLOOKUP(S74,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U74" s="23">
+      <c r="U74" s="24">
         <f>_xlfn.XLOOKUP(S74,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7062,11 +10412,11 @@
         <f>TRIM(CLEAN(PROPER(C75)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M75" s="21" t="str">
+      <c r="M75" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Gonzalez</v>
       </c>
-      <c r="N75" s="21" t="str">
+      <c r="N75" s="22" t="str">
         <f>_xlfn.XLOOKUP(O75,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -7094,7 +10444,7 @@
         <f>_xlfn.XLOOKUP(S75,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U75" s="23">
+      <c r="U75" s="24">
         <f>_xlfn.XLOOKUP(S75,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -7140,11 +10490,11 @@
         <f>TRIM(CLEAN(PROPER(C76)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M76" s="21" t="str">
+      <c r="M76" s="22" t="str">
         <f t="shared" si="3"/>
         <v>David Wilson</v>
       </c>
-      <c r="N76" s="21" t="str">
+      <c r="N76" s="22" t="str">
         <f>_xlfn.XLOOKUP(O76,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -7172,7 +10522,7 @@
         <f>_xlfn.XLOOKUP(S76,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U76" s="23">
+      <c r="U76" s="24">
         <f>_xlfn.XLOOKUP(S76,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -7218,11 +10568,11 @@
         <f>TRIM(CLEAN(PROPER(C77)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M77" s="21" t="str">
+      <c r="M77" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Gonzalez</v>
       </c>
-      <c r="N77" s="21" t="str">
+      <c r="N77" s="22" t="str">
         <f>_xlfn.XLOOKUP(O77,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -7250,7 +10600,7 @@
         <f>_xlfn.XLOOKUP(S77,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U77" s="23">
+      <c r="U77" s="24">
         <f>_xlfn.XLOOKUP(S77,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -7296,11 +10646,11 @@
         <f>TRIM(CLEAN(PROPER(C78)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M78" s="21" t="str">
+      <c r="M78" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Rodriguez</v>
       </c>
-      <c r="N78" s="21" t="str">
+      <c r="N78" s="22" t="str">
         <f>_xlfn.XLOOKUP(O78,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -7328,7 +10678,7 @@
         <f>_xlfn.XLOOKUP(S78,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U78" s="23">
+      <c r="U78" s="24">
         <f>_xlfn.XLOOKUP(S78,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -7374,11 +10724,11 @@
         <f>TRIM(CLEAN(PROPER(C79)))</f>
         <v>Miller</v>
       </c>
-      <c r="M79" s="21" t="str">
+      <c r="M79" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Emily Miller</v>
       </c>
-      <c r="N79" s="21" t="str">
+      <c r="N79" s="22" t="str">
         <f>_xlfn.XLOOKUP(O79,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -7406,7 +10756,7 @@
         <f>_xlfn.XLOOKUP(S79,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U79" s="23">
+      <c r="U79" s="24">
         <f>_xlfn.XLOOKUP(S79,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7449,11 +10799,11 @@
         <f>TRIM(CLEAN(PROPER(C80)))</f>
         <v>Miller</v>
       </c>
-      <c r="M80" s="21" t="str">
+      <c r="M80" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Sarah Miller</v>
       </c>
-      <c r="N80" s="21" t="str">
+      <c r="N80" s="22" t="str">
         <f>_xlfn.XLOOKUP(O80,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -7481,7 +10831,7 @@
         <f>_xlfn.XLOOKUP(S80,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U80" s="23">
+      <c r="U80" s="24">
         <f>_xlfn.XLOOKUP(S80,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -7527,11 +10877,11 @@
         <f>TRIM(CLEAN(PROPER(C81)))</f>
         <v>Garcia</v>
       </c>
-      <c r="M81" s="21" t="str">
+      <c r="M81" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jessica Garcia</v>
       </c>
-      <c r="N81" s="21" t="str">
+      <c r="N81" s="22" t="str">
         <f>_xlfn.XLOOKUP(O81,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -7559,7 +10909,7 @@
         <f>_xlfn.XLOOKUP(S81,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U81" s="23">
+      <c r="U81" s="24">
         <f>_xlfn.XLOOKUP(S81,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7605,11 +10955,11 @@
         <f>TRIM(CLEAN(PROPER(C82)))</f>
         <v>Smith</v>
       </c>
-      <c r="M82" s="21" t="str">
+      <c r="M82" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Richard Smith</v>
       </c>
-      <c r="N82" s="21" t="str">
+      <c r="N82" s="22" t="str">
         <f>_xlfn.XLOOKUP(O82,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -7637,7 +10987,7 @@
         <f>_xlfn.XLOOKUP(S82,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U82" s="23">
+      <c r="U82" s="24">
         <f>_xlfn.XLOOKUP(S82,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -7683,11 +11033,11 @@
         <f>TRIM(CLEAN(PROPER(C83)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M83" s="21" t="str">
+      <c r="M83" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Wilson</v>
       </c>
-      <c r="N83" s="21" t="str">
+      <c r="N83" s="22" t="str">
         <f>_xlfn.XLOOKUP(O83,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -7715,7 +11065,7 @@
         <f>_xlfn.XLOOKUP(S83,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U83" s="23">
+      <c r="U83" s="24">
         <f>_xlfn.XLOOKUP(S83,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7759,11 +11109,11 @@
         <f>TRIM(CLEAN(PROPER(C84)))</f>
         <v>Williams</v>
       </c>
-      <c r="M84" s="21" t="str">
+      <c r="M84" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Thomas Williams</v>
       </c>
-      <c r="N84" s="21" t="str">
+      <c r="N84" s="22" t="str">
         <f>_xlfn.XLOOKUP(O84,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -7791,7 +11141,7 @@
         <f>_xlfn.XLOOKUP(S84,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U84" s="23">
+      <c r="U84" s="24">
         <f>_xlfn.XLOOKUP(S84,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -7834,11 +11184,11 @@
         <f>TRIM(CLEAN(PROPER(C85)))</f>
         <v>Williams</v>
       </c>
-      <c r="M85" s="21" t="str">
+      <c r="M85" s="22" t="str">
         <f t="shared" si="3"/>
         <v>David Williams</v>
       </c>
-      <c r="N85" s="21" t="str">
+      <c r="N85" s="22" t="str">
         <f>_xlfn.XLOOKUP(O85,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -7866,7 +11216,7 @@
         <f>_xlfn.XLOOKUP(S85,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U85" s="23">
+      <c r="U85" s="24">
         <f>_xlfn.XLOOKUP(S85,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7912,11 +11262,11 @@
         <f>TRIM(CLEAN(PROPER(C86)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M86" s="21" t="str">
+      <c r="M86" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Johnson</v>
       </c>
-      <c r="N86" s="21" t="str">
+      <c r="N86" s="22" t="str">
         <f>_xlfn.XLOOKUP(O86,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -7944,7 +11294,7 @@
         <f>_xlfn.XLOOKUP(S86,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U86" s="23">
+      <c r="U86" s="24">
         <f>_xlfn.XLOOKUP(S86,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -7990,11 +11340,11 @@
         <f>TRIM(CLEAN(PROPER(C87)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M87" s="21" t="str">
+      <c r="M87" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Richard Gonzalez</v>
       </c>
-      <c r="N87" s="21" t="str">
+      <c r="N87" s="22" t="str">
         <f>_xlfn.XLOOKUP(O87,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -8022,7 +11372,7 @@
         <f>_xlfn.XLOOKUP(S87,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U87" s="23">
+      <c r="U87" s="24">
         <f>_xlfn.XLOOKUP(S87,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -8068,11 +11418,11 @@
         <f>TRIM(CLEAN(PROPER(C88)))</f>
         <v>Anderson</v>
       </c>
-      <c r="M88" s="21" t="str">
+      <c r="M88" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Anderson</v>
       </c>
-      <c r="N88" s="21" t="str">
+      <c r="N88" s="22" t="str">
         <f>_xlfn.XLOOKUP(O88,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -8100,7 +11450,7 @@
         <f>_xlfn.XLOOKUP(S88,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U88" s="23">
+      <c r="U88" s="24">
         <f>_xlfn.XLOOKUP(S88,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -8146,11 +11496,11 @@
         <f>TRIM(CLEAN(PROPER(C89)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M89" s="21" t="str">
+      <c r="M89" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Emily Gonzalez</v>
       </c>
-      <c r="N89" s="21" t="str">
+      <c r="N89" s="22" t="str">
         <f>_xlfn.XLOOKUP(O89,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -8178,7 +11528,7 @@
         <f>_xlfn.XLOOKUP(S89,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U89" s="23">
+      <c r="U89" s="24">
         <f>_xlfn.XLOOKUP(S89,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -8224,11 +11574,11 @@
         <f>TRIM(CLEAN(PROPER(C90)))</f>
         <v>Davis</v>
       </c>
-      <c r="M90" s="21" t="str">
+      <c r="M90" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Davis</v>
       </c>
-      <c r="N90" s="21" t="str">
+      <c r="N90" s="22" t="str">
         <f>_xlfn.XLOOKUP(O90,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -8256,7 +11606,7 @@
         <f>_xlfn.XLOOKUP(S90,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U90" s="23">
+      <c r="U90" s="24">
         <f>_xlfn.XLOOKUP(S90,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -8302,11 +11652,11 @@
         <f>TRIM(CLEAN(PROPER(C91)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M91" s="21" t="str">
+      <c r="M91" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Gonzalez</v>
       </c>
-      <c r="N91" s="21" t="str">
+      <c r="N91" s="22" t="str">
         <f>_xlfn.XLOOKUP(O91,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -8334,7 +11684,7 @@
         <f>_xlfn.XLOOKUP(S91,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U91" s="23">
+      <c r="U91" s="24">
         <f>_xlfn.XLOOKUP(S91,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -8380,11 +11730,11 @@
         <f>TRIM(CLEAN(PROPER(C92)))</f>
         <v>Jones</v>
       </c>
-      <c r="M92" s="21" t="str">
+      <c r="M92" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Thomas Jones</v>
       </c>
-      <c r="N92" s="21" t="str">
+      <c r="N92" s="22" t="str">
         <f>_xlfn.XLOOKUP(O92,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -8412,7 +11762,7 @@
         <f>_xlfn.XLOOKUP(S92,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U92" s="23">
+      <c r="U92" s="24">
         <f>_xlfn.XLOOKUP(S92,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -8458,11 +11808,11 @@
         <f>TRIM(CLEAN(PROPER(C93)))</f>
         <v>Anderson</v>
       </c>
-      <c r="M93" s="21" t="str">
+      <c r="M93" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jessica Anderson</v>
       </c>
-      <c r="N93" s="21" t="str">
+      <c r="N93" s="22" t="str">
         <f>_xlfn.XLOOKUP(O93,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -8490,7 +11840,7 @@
         <f>_xlfn.XLOOKUP(S93,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U93" s="23">
+      <c r="U93" s="24">
         <f>_xlfn.XLOOKUP(S93,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -8536,11 +11886,11 @@
         <f>TRIM(CLEAN(PROPER(C94)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M94" s="21" t="str">
+      <c r="M94" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Johnson</v>
       </c>
-      <c r="N94" s="21" t="str">
+      <c r="N94" s="22" t="str">
         <f>_xlfn.XLOOKUP(O94,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -8568,7 +11918,7 @@
         <f>_xlfn.XLOOKUP(S94,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U94" s="23">
+      <c r="U94" s="24">
         <f>_xlfn.XLOOKUP(S94,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -8614,11 +11964,11 @@
         <f>TRIM(CLEAN(PROPER(C95)))</f>
         <v>Miller</v>
       </c>
-      <c r="M95" s="21" t="str">
+      <c r="M95" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Thomas Miller</v>
       </c>
-      <c r="N95" s="21" t="str">
+      <c r="N95" s="22" t="str">
         <f>_xlfn.XLOOKUP(O95,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -8646,7 +11996,7 @@
         <f>_xlfn.XLOOKUP(S95,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U95" s="23">
+      <c r="U95" s="24">
         <f>_xlfn.XLOOKUP(S95,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -8692,11 +12042,11 @@
         <f>TRIM(CLEAN(PROPER(C96)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M96" s="21" t="str">
+      <c r="M96" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Gonzalez</v>
       </c>
-      <c r="N96" s="21" t="str">
+      <c r="N96" s="22" t="str">
         <f>_xlfn.XLOOKUP(O96,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -8724,7 +12074,7 @@
         <f>_xlfn.XLOOKUP(S96,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U96" s="23">
+      <c r="U96" s="24">
         <f>_xlfn.XLOOKUP(S96,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -8738,7 +12088,7 @@
         <v>178</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>29</v>
@@ -8770,11 +12120,11 @@
         <f>TRIM(CLEAN(PROPER(C97)))</f>
         <v>Smith</v>
       </c>
-      <c r="M97" s="21" t="str">
+      <c r="M97" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Unknown Smith</v>
       </c>
-      <c r="N97" s="21" t="str">
+      <c r="N97" s="22" t="str">
         <f>_xlfn.XLOOKUP(O97,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -8802,7 +12152,7 @@
         <f>_xlfn.XLOOKUP(S97,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U97" s="23">
+      <c r="U97" s="24">
         <f>_xlfn.XLOOKUP(S97,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -8848,11 +12198,11 @@
         <f>TRIM(CLEAN(PROPER(C98)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M98" s="21" t="str">
+      <c r="M98" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Johnson</v>
       </c>
-      <c r="N98" s="21" t="str">
+      <c r="N98" s="22" t="str">
         <f>_xlfn.XLOOKUP(O98,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -8880,7 +12230,7 @@
         <f>_xlfn.XLOOKUP(S98,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U98" s="23">
+      <c r="U98" s="24">
         <f>_xlfn.XLOOKUP(S98,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -8926,11 +12276,11 @@
         <f>TRIM(CLEAN(PROPER(C99)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M99" s="21" t="str">
+      <c r="M99" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Johnson</v>
       </c>
-      <c r="N99" s="21" t="str">
+      <c r="N99" s="22" t="str">
         <f>_xlfn.XLOOKUP(O99,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -8958,7 +12308,7 @@
         <f>_xlfn.XLOOKUP(S99,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U99" s="23">
+      <c r="U99" s="24">
         <f>_xlfn.XLOOKUP(S99,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9001,11 +12351,11 @@
         <f>TRIM(CLEAN(PROPER(C100)))</f>
         <v>Jones</v>
       </c>
-      <c r="M100" s="21" t="str">
+      <c r="M100" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Jones</v>
       </c>
-      <c r="N100" s="21" t="str">
+      <c r="N100" s="22" t="str">
         <f>_xlfn.XLOOKUP(O100,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -9033,7 +12383,7 @@
         <f>_xlfn.XLOOKUP(S100,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U100" s="23">
+      <c r="U100" s="24">
         <f>_xlfn.XLOOKUP(S100,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9079,11 +12429,11 @@
         <f>TRIM(CLEAN(PROPER(C101)))</f>
         <v>Lopez</v>
       </c>
-      <c r="M101" s="21" t="str">
+      <c r="M101" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Lopez</v>
       </c>
-      <c r="N101" s="21" t="str">
+      <c r="N101" s="22" t="str">
         <f>_xlfn.XLOOKUP(O101,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -9111,7 +12461,7 @@
         <f>_xlfn.XLOOKUP(S101,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U101" s="23">
+      <c r="U101" s="24">
         <f>_xlfn.XLOOKUP(S101,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9157,11 +12507,11 @@
         <f>TRIM(CLEAN(PROPER(C102)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M102" s="21" t="str">
+      <c r="M102" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Gonzalez</v>
       </c>
-      <c r="N102" s="21" t="str">
+      <c r="N102" s="22" t="str">
         <f>_xlfn.XLOOKUP(O102,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -9189,7 +12539,7 @@
         <f>_xlfn.XLOOKUP(S102,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U102" s="23">
+      <c r="U102" s="24">
         <f>_xlfn.XLOOKUP(S102,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -9235,11 +12585,11 @@
         <f>TRIM(CLEAN(PROPER(C103)))</f>
         <v>Davis</v>
       </c>
-      <c r="M103" s="21" t="str">
+      <c r="M103" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Davis</v>
       </c>
-      <c r="N103" s="21" t="str">
+      <c r="N103" s="22" t="str">
         <f>_xlfn.XLOOKUP(O103,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -9267,7 +12617,7 @@
         <f>_xlfn.XLOOKUP(S103,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U103" s="23">
+      <c r="U103" s="24">
         <f>_xlfn.XLOOKUP(S103,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -9313,11 +12663,11 @@
         <f>TRIM(CLEAN(PROPER(C104)))</f>
         <v>Smith</v>
       </c>
-      <c r="M104" s="21" t="str">
+      <c r="M104" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Smith</v>
       </c>
-      <c r="N104" s="21" t="str">
+      <c r="N104" s="22" t="str">
         <f>_xlfn.XLOOKUP(O104,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -9345,7 +12695,7 @@
         <f>_xlfn.XLOOKUP(S104,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U104" s="23">
+      <c r="U104" s="24">
         <f>_xlfn.XLOOKUP(S104,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -9391,11 +12741,11 @@
         <f>TRIM(CLEAN(PROPER(C105)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M105" s="21" t="str">
+      <c r="M105" s="22" t="str">
         <f t="shared" si="3"/>
         <v>James Gonzalez</v>
       </c>
-      <c r="N105" s="21" t="str">
+      <c r="N105" s="22" t="str">
         <f>_xlfn.XLOOKUP(O105,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -9423,7 +12773,7 @@
         <f>_xlfn.XLOOKUP(S105,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U105" s="23">
+      <c r="U105" s="24">
         <f>_xlfn.XLOOKUP(S105,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -9469,11 +12819,11 @@
         <f>TRIM(CLEAN(PROPER(C106)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M106" s="21" t="str">
+      <c r="M106" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Emily Johnson</v>
       </c>
-      <c r="N106" s="21" t="str">
+      <c r="N106" s="22" t="str">
         <f>_xlfn.XLOOKUP(O106,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -9501,7 +12851,7 @@
         <f>_xlfn.XLOOKUP(S106,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U106" s="23">
+      <c r="U106" s="24">
         <f>_xlfn.XLOOKUP(S106,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9547,11 +12897,11 @@
         <f>TRIM(CLEAN(PROPER(C107)))</f>
         <v>Williams</v>
       </c>
-      <c r="M107" s="21" t="str">
+      <c r="M107" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Williams</v>
       </c>
-      <c r="N107" s="21" t="str">
+      <c r="N107" s="22" t="str">
         <f>_xlfn.XLOOKUP(O107,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -9579,7 +12929,7 @@
         <f>_xlfn.XLOOKUP(S107,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U107" s="23">
+      <c r="U107" s="24">
         <f>_xlfn.XLOOKUP(S107,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9625,11 +12975,11 @@
         <f>TRIM(CLEAN(PROPER(C108)))</f>
         <v>Jones</v>
       </c>
-      <c r="M108" s="21" t="str">
+      <c r="M108" s="22" t="str">
         <f t="shared" si="3"/>
         <v>James Jones</v>
       </c>
-      <c r="N108" s="21" t="str">
+      <c r="N108" s="22" t="str">
         <f>_xlfn.XLOOKUP(O108,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -9657,7 +13007,7 @@
         <f>_xlfn.XLOOKUP(S108,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U108" s="23">
+      <c r="U108" s="24">
         <f>_xlfn.XLOOKUP(S108,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -9701,11 +13051,11 @@
         <f>TRIM(CLEAN(PROPER(C109)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M109" s="21" t="str">
+      <c r="M109" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jessica Gonzalez</v>
       </c>
-      <c r="N109" s="21" t="str">
+      <c r="N109" s="22" t="str">
         <f>_xlfn.XLOOKUP(O109,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -9733,7 +13083,7 @@
         <f>_xlfn.XLOOKUP(S109,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U109" s="23">
+      <c r="U109" s="24">
         <f>_xlfn.XLOOKUP(S109,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -9779,11 +13129,11 @@
         <f>TRIM(CLEAN(PROPER(C110)))</f>
         <v>Miller</v>
       </c>
-      <c r="M110" s="21" t="str">
+      <c r="M110" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Sarah Miller</v>
       </c>
-      <c r="N110" s="21" t="str">
+      <c r="N110" s="22" t="str">
         <f>_xlfn.XLOOKUP(O110,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -9811,7 +13161,7 @@
         <f>_xlfn.XLOOKUP(S110,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U110" s="23">
+      <c r="U110" s="24">
         <f>_xlfn.XLOOKUP(S110,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -9857,11 +13207,11 @@
         <f>TRIM(CLEAN(PROPER(C111)))</f>
         <v>Smith</v>
       </c>
-      <c r="M111" s="21" t="str">
+      <c r="M111" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jessica Smith</v>
       </c>
-      <c r="N111" s="21" t="str">
+      <c r="N111" s="22" t="str">
         <f>_xlfn.XLOOKUP(O111,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -9889,7 +13239,7 @@
         <f>_xlfn.XLOOKUP(S111,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U111" s="23">
+      <c r="U111" s="24">
         <f>_xlfn.XLOOKUP(S111,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -9935,11 +13285,11 @@
         <f>TRIM(CLEAN(PROPER(C112)))</f>
         <v>Jones</v>
       </c>
-      <c r="M112" s="21" t="str">
+      <c r="M112" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Thomas Jones</v>
       </c>
-      <c r="N112" s="21" t="str">
+      <c r="N112" s="22" t="str">
         <f>_xlfn.XLOOKUP(O112,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -9967,7 +13317,7 @@
         <f>_xlfn.XLOOKUP(S112,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U112" s="23">
+      <c r="U112" s="24">
         <f>_xlfn.XLOOKUP(S112,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10013,11 +13363,11 @@
         <f>TRIM(CLEAN(PROPER(C113)))</f>
         <v>Brown</v>
       </c>
-      <c r="M113" s="21" t="str">
+      <c r="M113" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Amanda Brown</v>
       </c>
-      <c r="N113" s="21" t="str">
+      <c r="N113" s="22" t="str">
         <f>_xlfn.XLOOKUP(O113,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -10045,7 +13395,7 @@
         <f>_xlfn.XLOOKUP(S113,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U113" s="23">
+      <c r="U113" s="24">
         <f>_xlfn.XLOOKUP(S113,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -10091,11 +13441,11 @@
         <f>TRIM(CLEAN(PROPER(C114)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M114" s="21" t="str">
+      <c r="M114" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Robert Martinez</v>
       </c>
-      <c r="N114" s="21" t="str">
+      <c r="N114" s="22" t="str">
         <f>_xlfn.XLOOKUP(O114,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -10123,7 +13473,7 @@
         <f>_xlfn.XLOOKUP(S114,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U114" s="23">
+      <c r="U114" s="24">
         <f>_xlfn.XLOOKUP(S114,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -10169,11 +13519,11 @@
         <f>TRIM(CLEAN(PROPER(C115)))</f>
         <v>Miller</v>
       </c>
-      <c r="M115" s="21" t="str">
+      <c r="M115" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Thomas Miller</v>
       </c>
-      <c r="N115" s="21" t="str">
+      <c r="N115" s="22" t="str">
         <f>_xlfn.XLOOKUP(O115,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -10201,7 +13551,7 @@
         <f>_xlfn.XLOOKUP(S115,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U115" s="23">
+      <c r="U115" s="24">
         <f>_xlfn.XLOOKUP(S115,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10247,11 +13597,11 @@
         <f>TRIM(CLEAN(PROPER(C116)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M116" s="21" t="str">
+      <c r="M116" s="22" t="str">
         <f t="shared" si="3"/>
         <v>David Rodriguez</v>
       </c>
-      <c r="N116" s="21" t="str">
+      <c r="N116" s="22" t="str">
         <f>_xlfn.XLOOKUP(O116,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -10279,7 +13629,7 @@
         <f>_xlfn.XLOOKUP(S116,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U116" s="23">
+      <c r="U116" s="24">
         <f>_xlfn.XLOOKUP(S116,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -10325,11 +13675,11 @@
         <f>TRIM(CLEAN(PROPER(C117)))</f>
         <v>Miller</v>
       </c>
-      <c r="M117" s="21" t="str">
+      <c r="M117" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Miller</v>
       </c>
-      <c r="N117" s="21" t="str">
+      <c r="N117" s="22" t="str">
         <f>_xlfn.XLOOKUP(O117,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -10357,7 +13707,7 @@
         <f>_xlfn.XLOOKUP(S117,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U117" s="23">
+      <c r="U117" s="24">
         <f>_xlfn.XLOOKUP(S117,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10403,11 +13753,11 @@
         <f>TRIM(CLEAN(PROPER(C118)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M118" s="21" t="str">
+      <c r="M118" s="22" t="str">
         <f t="shared" si="3"/>
         <v>James Rodriguez</v>
       </c>
-      <c r="N118" s="21" t="str">
+      <c r="N118" s="22" t="str">
         <f>_xlfn.XLOOKUP(O118,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -10435,7 +13785,7 @@
         <f>_xlfn.XLOOKUP(S118,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U118" s="23">
+      <c r="U118" s="24">
         <f>_xlfn.XLOOKUP(S118,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10481,11 +13831,11 @@
         <f>TRIM(CLEAN(PROPER(C119)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M119" s="21" t="str">
+      <c r="M119" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Sarah Rodriguez</v>
       </c>
-      <c r="N119" s="21" t="str">
+      <c r="N119" s="22" t="str">
         <f>_xlfn.XLOOKUP(O119,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -10513,7 +13863,7 @@
         <f>_xlfn.XLOOKUP(S119,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U119" s="23">
+      <c r="U119" s="24">
         <f>_xlfn.XLOOKUP(S119,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10556,11 +13906,11 @@
         <f>TRIM(CLEAN(PROPER(C120)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M120" s="21" t="str">
+      <c r="M120" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Sarah Wilson</v>
       </c>
-      <c r="N120" s="21" t="str">
+      <c r="N120" s="22" t="str">
         <f>_xlfn.XLOOKUP(O120,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -10588,7 +13938,7 @@
         <f>_xlfn.XLOOKUP(S120,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U120" s="23">
+      <c r="U120" s="24">
         <f>_xlfn.XLOOKUP(S120,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10631,11 +13981,11 @@
         <f>TRIM(CLEAN(PROPER(C121)))</f>
         <v>Brown</v>
       </c>
-      <c r="M121" s="21" t="str">
+      <c r="M121" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Brown</v>
       </c>
-      <c r="N121" s="21" t="str">
+      <c r="N121" s="22" t="str">
         <f>_xlfn.XLOOKUP(O121,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -10663,7 +14013,7 @@
         <f>_xlfn.XLOOKUP(S121,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U121" s="23">
+      <c r="U121" s="24">
         <f>_xlfn.XLOOKUP(S121,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -10706,11 +14056,11 @@
         <f>TRIM(CLEAN(PROPER(C122)))</f>
         <v>Williams</v>
       </c>
-      <c r="M122" s="21" t="str">
+      <c r="M122" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Robert Williams</v>
       </c>
-      <c r="N122" s="21" t="str">
+      <c r="N122" s="22" t="str">
         <f>_xlfn.XLOOKUP(O122,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -10738,7 +14088,7 @@
         <f>_xlfn.XLOOKUP(S122,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U122" s="23">
+      <c r="U122" s="24">
         <f>_xlfn.XLOOKUP(S122,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -10784,11 +14134,11 @@
         <f>TRIM(CLEAN(PROPER(C123)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M123" s="21" t="str">
+      <c r="M123" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Melissa Rodriguez</v>
       </c>
-      <c r="N123" s="21" t="str">
+      <c r="N123" s="22" t="str">
         <f>_xlfn.XLOOKUP(O123,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -10816,7 +14166,7 @@
         <f>_xlfn.XLOOKUP(S123,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U123" s="23">
+      <c r="U123" s="24">
         <f>_xlfn.XLOOKUP(S123,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -10862,11 +14212,11 @@
         <f>TRIM(CLEAN(PROPER(C124)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M124" s="21" t="str">
+      <c r="M124" s="22" t="str">
         <f t="shared" si="3"/>
         <v>James Johnson</v>
       </c>
-      <c r="N124" s="21" t="str">
+      <c r="N124" s="22" t="str">
         <f>_xlfn.XLOOKUP(O124,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -10894,7 +14244,7 @@
         <f>_xlfn.XLOOKUP(S124,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U124" s="23">
+      <c r="U124" s="24">
         <f>_xlfn.XLOOKUP(S124,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -10940,11 +14290,11 @@
         <f>TRIM(CLEAN(PROPER(C125)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M125" s="21" t="str">
+      <c r="M125" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Michael Wilson</v>
       </c>
-      <c r="N125" s="21" t="str">
+      <c r="N125" s="22" t="str">
         <f>_xlfn.XLOOKUP(O125,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -10972,7 +14322,7 @@
         <f>_xlfn.XLOOKUP(S125,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U125" s="23">
+      <c r="U125" s="24">
         <f>_xlfn.XLOOKUP(S125,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -11018,11 +14368,11 @@
         <f>TRIM(CLEAN(PROPER(C126)))</f>
         <v>Jones</v>
       </c>
-      <c r="M126" s="21" t="str">
+      <c r="M126" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Jones</v>
       </c>
-      <c r="N126" s="21" t="str">
+      <c r="N126" s="22" t="str">
         <f>_xlfn.XLOOKUP(O126,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -11050,7 +14400,7 @@
         <f>_xlfn.XLOOKUP(S126,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U126" s="23">
+      <c r="U126" s="24">
         <f>_xlfn.XLOOKUP(S126,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -11096,11 +14446,11 @@
         <f>TRIM(CLEAN(PROPER(C127)))</f>
         <v>Williams</v>
       </c>
-      <c r="M127" s="21" t="str">
+      <c r="M127" s="22" t="str">
         <f t="shared" si="3"/>
         <v>William Williams</v>
       </c>
-      <c r="N127" s="21" t="str">
+      <c r="N127" s="22" t="str">
         <f>_xlfn.XLOOKUP(O127,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -11128,7 +14478,7 @@
         <f>_xlfn.XLOOKUP(S127,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U127" s="23">
+      <c r="U127" s="24">
         <f>_xlfn.XLOOKUP(S127,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -11174,11 +14524,11 @@
         <f>TRIM(CLEAN(PROPER(C128)))</f>
         <v>Williams</v>
       </c>
-      <c r="M128" s="21" t="str">
+      <c r="M128" s="22" t="str">
         <f t="shared" si="3"/>
         <v>David Williams</v>
       </c>
-      <c r="N128" s="21" t="str">
+      <c r="N128" s="22" t="str">
         <f>_xlfn.XLOOKUP(O128,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -11206,7 +14556,7 @@
         <f>_xlfn.XLOOKUP(S128,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U128" s="23">
+      <c r="U128" s="24">
         <f>_xlfn.XLOOKUP(S128,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -11252,11 +14602,11 @@
         <f>TRIM(CLEAN(PROPER(C129)))</f>
         <v>Davis</v>
       </c>
-      <c r="M129" s="21" t="str">
+      <c r="M129" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Jane Davis</v>
       </c>
-      <c r="N129" s="21" t="str">
+      <c r="N129" s="22" t="str">
         <f>_xlfn.XLOOKUP(O129,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -11284,7 +14634,7 @@
         <f>_xlfn.XLOOKUP(S129,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U129" s="23">
+      <c r="U129" s="24">
         <f>_xlfn.XLOOKUP(S129,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -11330,11 +14680,11 @@
         <f>TRIM(CLEAN(PROPER(C130)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M130" s="21" t="str">
+      <c r="M130" s="22" t="str">
         <f t="shared" si="3"/>
         <v>John Martinez</v>
       </c>
-      <c r="N130" s="21" t="str">
+      <c r="N130" s="22" t="str">
         <f>_xlfn.XLOOKUP(O130,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -11362,7 +14712,7 @@
         <f>_xlfn.XLOOKUP(S130,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U130" s="23">
+      <c r="U130" s="24">
         <f>_xlfn.XLOOKUP(S130,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -11408,11 +14758,11 @@
         <f>TRIM(CLEAN(PROPER(C131)))</f>
         <v>Anderson</v>
       </c>
-      <c r="M131" s="21" t="str">
+      <c r="M131" s="22" t="str">
         <f t="shared" ref="M131:M151" si="6">_xlfn.TEXTJOIN(" ",TRUE,K131,L131)</f>
         <v>David Anderson</v>
       </c>
-      <c r="N131" s="21" t="str">
+      <c r="N131" s="22" t="str">
         <f>_xlfn.XLOOKUP(O131,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -11440,7 +14790,7 @@
         <f>_xlfn.XLOOKUP(S131,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U131" s="23">
+      <c r="U131" s="24">
         <f>_xlfn.XLOOKUP(S131,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -11486,11 +14836,11 @@
         <f>TRIM(CLEAN(PROPER(C132)))</f>
         <v>Smith</v>
       </c>
-      <c r="M132" s="21" t="str">
+      <c r="M132" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Sarah Smith</v>
       </c>
-      <c r="N132" s="21" t="str">
+      <c r="N132" s="22" t="str">
         <f>_xlfn.XLOOKUP(O132,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -11518,7 +14868,7 @@
         <f>_xlfn.XLOOKUP(S132,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U132" s="23">
+      <c r="U132" s="24">
         <f>_xlfn.XLOOKUP(S132,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -11562,11 +14912,11 @@
         <f>TRIM(CLEAN(PROPER(C133)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M133" s="21" t="str">
+      <c r="M133" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Melissa Hernandez</v>
       </c>
-      <c r="N133" s="21" t="str">
+      <c r="N133" s="22" t="str">
         <f>_xlfn.XLOOKUP(O133,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -11594,7 +14944,7 @@
         <f>_xlfn.XLOOKUP(S133,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U133" s="23">
+      <c r="U133" s="24">
         <f>_xlfn.XLOOKUP(S133,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -11640,11 +14990,11 @@
         <f>TRIM(CLEAN(PROPER(C134)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M134" s="21" t="str">
+      <c r="M134" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Melissa Johnson</v>
       </c>
-      <c r="N134" s="21" t="str">
+      <c r="N134" s="22" t="str">
         <f>_xlfn.XLOOKUP(O134,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -11672,7 +15022,7 @@
         <f>_xlfn.XLOOKUP(S134,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U134" s="23">
+      <c r="U134" s="24">
         <f>_xlfn.XLOOKUP(S134,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -11718,11 +15068,11 @@
         <f>TRIM(CLEAN(PROPER(C135)))</f>
         <v>Garcia</v>
       </c>
-      <c r="M135" s="21" t="str">
+      <c r="M135" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Jane Garcia</v>
       </c>
-      <c r="N135" s="21" t="str">
+      <c r="N135" s="22" t="str">
         <f>_xlfn.XLOOKUP(O135,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -11750,7 +15100,7 @@
         <f>_xlfn.XLOOKUP(S135,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="U135" s="23">
+      <c r="U135" s="24">
         <f>_xlfn.XLOOKUP(S135,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0</v>
       </c>
@@ -11796,11 +15146,11 @@
         <f>TRIM(CLEAN(PROPER(C136)))</f>
         <v>Davis</v>
       </c>
-      <c r="M136" s="21" t="str">
+      <c r="M136" s="22" t="str">
         <f t="shared" si="6"/>
         <v>David Davis</v>
       </c>
-      <c r="N136" s="21" t="str">
+      <c r="N136" s="22" t="str">
         <f>_xlfn.XLOOKUP(O136,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -11828,7 +15178,7 @@
         <f>_xlfn.XLOOKUP(S136,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U136" s="23">
+      <c r="U136" s="24">
         <f>_xlfn.XLOOKUP(S136,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -11871,11 +15221,11 @@
         <f>TRIM(CLEAN(PROPER(C137)))</f>
         <v>Wilson</v>
       </c>
-      <c r="M137" s="21" t="str">
+      <c r="M137" s="22" t="str">
         <f t="shared" si="6"/>
         <v>James Wilson</v>
       </c>
-      <c r="N137" s="21" t="str">
+      <c r="N137" s="22" t="str">
         <f>_xlfn.XLOOKUP(O137,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -11903,7 +15253,7 @@
         <f>_xlfn.XLOOKUP(S137,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U137" s="23">
+      <c r="U137" s="24">
         <f>_xlfn.XLOOKUP(S137,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -11949,11 +15299,11 @@
         <f>TRIM(CLEAN(PROPER(C138)))</f>
         <v>Johnson</v>
       </c>
-      <c r="M138" s="21" t="str">
+      <c r="M138" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Richard Johnson</v>
       </c>
-      <c r="N138" s="21" t="str">
+      <c r="N138" s="22" t="str">
         <f>_xlfn.XLOOKUP(O138,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -11981,7 +15331,7 @@
         <f>_xlfn.XLOOKUP(S138,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U138" s="23">
+      <c r="U138" s="24">
         <f>_xlfn.XLOOKUP(S138,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12024,11 +15374,11 @@
         <f>TRIM(CLEAN(PROPER(C139)))</f>
         <v>Williams</v>
       </c>
-      <c r="M139" s="21" t="str">
+      <c r="M139" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Richard Williams</v>
       </c>
-      <c r="N139" s="21" t="str">
+      <c r="N139" s="22" t="str">
         <f>_xlfn.XLOOKUP(O139,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -12056,7 +15406,7 @@
         <f>_xlfn.XLOOKUP(S139,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U139" s="23">
+      <c r="U139" s="24">
         <f>_xlfn.XLOOKUP(S139,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12102,11 +15452,11 @@
         <f>TRIM(CLEAN(PROPER(C140)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M140" s="21" t="str">
+      <c r="M140" s="22" t="str">
         <f t="shared" si="6"/>
         <v>John Hernandez</v>
       </c>
-      <c r="N140" s="21" t="str">
+      <c r="N140" s="22" t="str">
         <f>_xlfn.XLOOKUP(O140,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -12134,7 +15484,7 @@
         <f>_xlfn.XLOOKUP(S140,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Achieving</v>
       </c>
-      <c r="U140" s="23">
+      <c r="U140" s="24">
         <f>_xlfn.XLOOKUP(S140,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.05</v>
       </c>
@@ -12180,11 +15530,11 @@
         <f>TRIM(CLEAN(PROPER(C141)))</f>
         <v>Gonzalez</v>
       </c>
-      <c r="M141" s="21" t="str">
+      <c r="M141" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Sarah Gonzalez</v>
       </c>
-      <c r="N141" s="21" t="str">
+      <c r="N141" s="22" t="str">
         <f>_xlfn.XLOOKUP(O141,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -12212,7 +15562,7 @@
         <f>_xlfn.XLOOKUP(S141,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U141" s="23">
+      <c r="U141" s="24">
         <f>_xlfn.XLOOKUP(S141,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12255,11 +15605,11 @@
         <f>TRIM(CLEAN(PROPER(C142)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M142" s="21" t="str">
+      <c r="M142" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Melissa Hernandez</v>
       </c>
-      <c r="N142" s="21" t="str">
+      <c r="N142" s="22" t="str">
         <f>_xlfn.XLOOKUP(O142,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -12287,7 +15637,7 @@
         <f>_xlfn.XLOOKUP(S142,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U142" s="23">
+      <c r="U142" s="24">
         <f>_xlfn.XLOOKUP(S142,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12333,11 +15683,11 @@
         <f>TRIM(CLEAN(PROPER(C143)))</f>
         <v>Hernandez</v>
       </c>
-      <c r="M143" s="21" t="str">
+      <c r="M143" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Melissa Hernandez</v>
       </c>
-      <c r="N143" s="21" t="str">
+      <c r="N143" s="22" t="str">
         <f>_xlfn.XLOOKUP(O143,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -12365,7 +15715,7 @@
         <f>_xlfn.XLOOKUP(S143,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U143" s="23">
+      <c r="U143" s="24">
         <f>_xlfn.XLOOKUP(S143,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -12408,11 +15758,11 @@
         <f>TRIM(CLEAN(PROPER(C144)))</f>
         <v>Davis</v>
       </c>
-      <c r="M144" s="21" t="str">
+      <c r="M144" s="22" t="str">
         <f t="shared" si="6"/>
         <v>John Davis</v>
       </c>
-      <c r="N144" s="21" t="str">
+      <c r="N144" s="22" t="str">
         <f>_xlfn.XLOOKUP(O144,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -12440,7 +15790,7 @@
         <f>_xlfn.XLOOKUP(S144,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U144" s="23">
+      <c r="U144" s="24">
         <f>_xlfn.XLOOKUP(S144,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12486,11 +15836,11 @@
         <f>TRIM(CLEAN(PROPER(C145)))</f>
         <v>Davis</v>
       </c>
-      <c r="M145" s="21" t="str">
+      <c r="M145" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Richard Davis</v>
       </c>
-      <c r="N145" s="21" t="str">
+      <c r="N145" s="22" t="str">
         <f>_xlfn.XLOOKUP(O145,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Human Resources</v>
       </c>
@@ -12518,7 +15868,7 @@
         <f>_xlfn.XLOOKUP(S145,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U145" s="23">
+      <c r="U145" s="24">
         <f>_xlfn.XLOOKUP(S145,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12532,7 +15882,7 @@
         <v>241</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>58</v>
@@ -12564,11 +15914,11 @@
         <f>TRIM(CLEAN(PROPER(C146)))</f>
         <v>Jones</v>
       </c>
-      <c r="M146" s="21" t="str">
+      <c r="M146" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Unknown Jones</v>
       </c>
-      <c r="N146" s="21" t="str">
+      <c r="N146" s="22" t="str">
         <f>_xlfn.XLOOKUP(O146,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -12596,7 +15946,7 @@
         <f>_xlfn.XLOOKUP(S146,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U146" s="23">
+      <c r="U146" s="24">
         <f>_xlfn.XLOOKUP(S146,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -12642,11 +15992,11 @@
         <f>TRIM(CLEAN(PROPER(C147)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M147" s="21" t="str">
+      <c r="M147" s="22" t="str">
         <f t="shared" si="6"/>
         <v>William Rodriguez</v>
       </c>
-      <c r="N147" s="21" t="str">
+      <c r="N147" s="22" t="str">
         <f>_xlfn.XLOOKUP(O147,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Finance</v>
       </c>
@@ -12674,7 +16024,7 @@
         <f>_xlfn.XLOOKUP(S147,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Exceeding</v>
       </c>
-      <c r="U147" s="23">
+      <c r="U147" s="24">
         <f>_xlfn.XLOOKUP(S147,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.08</v>
       </c>
@@ -12720,11 +16070,11 @@
         <f>TRIM(CLEAN(PROPER(C148)))</f>
         <v>Miller</v>
       </c>
-      <c r="M148" s="21" t="str">
+      <c r="M148" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Melissa Miller</v>
       </c>
-      <c r="N148" s="21" t="str">
+      <c r="N148" s="22" t="str">
         <f>_xlfn.XLOOKUP(O148,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Sales</v>
       </c>
@@ -12752,7 +16102,7 @@
         <f>_xlfn.XLOOKUP(S148,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U148" s="23">
+      <c r="U148" s="24">
         <f>_xlfn.XLOOKUP(S148,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12798,11 +16148,11 @@
         <f>TRIM(CLEAN(PROPER(C149)))</f>
         <v>Martinez</v>
       </c>
-      <c r="M149" s="21" t="str">
+      <c r="M149" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Emily Martinez</v>
       </c>
-      <c r="N149" s="21" t="str">
+      <c r="N149" s="22" t="str">
         <f>_xlfn.XLOOKUP(O149,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Operations</v>
       </c>
@@ -12830,7 +16180,7 @@
         <f>_xlfn.XLOOKUP(S149,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Outstanding</v>
       </c>
-      <c r="U149" s="23">
+      <c r="U149" s="24">
         <f>_xlfn.XLOOKUP(S149,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.12</v>
       </c>
@@ -12876,11 +16226,11 @@
         <f>TRIM(CLEAN(PROPER(C150)))</f>
         <v>Rodriguez</v>
       </c>
-      <c r="M150" s="21" t="str">
+      <c r="M150" s="22" t="str">
         <f t="shared" si="6"/>
         <v>James Rodriguez</v>
       </c>
-      <c r="N150" s="21" t="str">
+      <c r="N150" s="22" t="str">
         <f>_xlfn.XLOOKUP(O150,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Marketing</v>
       </c>
@@ -12908,7 +16258,7 @@
         <f>_xlfn.XLOOKUP(S150,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U150" s="23">
+      <c r="U150" s="24">
         <f>_xlfn.XLOOKUP(S150,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -12954,11 +16304,11 @@
         <f>TRIM(CLEAN(PROPER(C151)))</f>
         <v>Brown</v>
       </c>
-      <c r="M151" s="21" t="str">
+      <c r="M151" s="22" t="str">
         <f t="shared" si="6"/>
         <v>Amanda Brown</v>
       </c>
-      <c r="N151" s="21" t="str">
+      <c r="N151" s="22" t="str">
         <f>_xlfn.XLOOKUP(O151,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</f>
         <v>Information Technology</v>
       </c>
@@ -12986,7 +16336,7 @@
         <f>_xlfn.XLOOKUP(S151,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</f>
         <v>Developing</v>
       </c>
-      <c r="U151" s="23">
+      <c r="U151" s="24">
         <f>_xlfn.XLOOKUP(S151,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</f>
         <v>0.02</v>
       </c>
@@ -13061,10 +16411,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16911,7 +20264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16981,7 +20334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72CA07F-DF8D-4581-809B-F2D4A014C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E696B70-54DE-4417-8491-AC4FE504352C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -2,26 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A723916F-F97B-4603-85BC-2E77269C53AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7B919F-CD76-48B4-ADA5-E710E57B870E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="6" r:id="rId1"/>
-    <sheet name="Working_Data" sheetId="4" r:id="rId2"/>
-    <sheet name="Raw_Employee_Data" sheetId="1" r:id="rId3"/>
-    <sheet name="Lookup_Departments" sheetId="2" r:id="rId4"/>
-    <sheet name="Lookup_Performance" sheetId="3" r:id="rId5"/>
+    <sheet name="Analysis" sheetId="6" r:id="rId1"/>
+    <sheet name="Pivot_Charts" sheetId="7" r:id="rId2"/>
+    <sheet name="HR_Dashboard" sheetId="8" r:id="rId3"/>
+    <sheet name="Working_Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Raw_Employee_Data" sheetId="1" r:id="rId5"/>
+    <sheet name="Lookup_Departments" sheetId="2" r:id="rId6"/>
+    <sheet name="Lookup_Performance" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1063,12 +1065,6 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -1119,6 +1115,12 @@
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1130,6 +1132,7625 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Bonus Payout </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="narHorz">
+              <a:fgClr>
+                <a:schemeClr val="accent1"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:innerShdw blurRad="114300">
+                <a:schemeClr val="accent1"/>
+              </a:innerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$18:$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Achieving</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Developing</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Exceeding</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Needs Improvement</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Outstanding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$18:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.9500000000000011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0400000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2000000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D45C-4DC5-8542-360394E4F62D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="164"/>
+        <c:overlap val="-22"/>
+        <c:axId val="749678752"/>
+        <c:axId val="749676352"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="749678752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="749676352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="749676352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="749678752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="105"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="5"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!Headcount &amp; Average Salary by Department</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1200">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Headcount &amp; Average Salary by Department</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:tint val="77000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:shade val="76000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent3">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent3">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HeadCount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:tint val="77000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2F6C-4DBE-8FD7-A629F49F20B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average Salary</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:shade val="76000"/>
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                        <a:lumOff val="40000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>"₦"#,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>87938.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85649.941176470587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80014.258064516151</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>85508.166666666657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79786.666666666657</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87282.347826086945</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2F6C-4DBE-8FD7-A629F49F20B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="109259184"/>
+        <c:axId val="109261104"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="109259184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:noFill/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="109261104"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="109261104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="109259184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable3</c:name>
+    <c:fmtId val="7"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t> Attrition Rate </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$G$3:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ACTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$5:$F$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$G$5:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C395-491C-ABE9-10BA10D6CFEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$H$3:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LEFT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$5:$F$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$H$5:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C395-491C-ABE9-10BA10D6CFEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$I$3:$I$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RESIGNED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$5:$F$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$I$5:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C395-491C-ABE9-10BA10D6CFEF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="412426144"/>
+        <c:axId val="412422304"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="412426144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="412422304"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="412422304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="412426144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable2</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Bonus Payout </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="narHorz">
+              <a:fgClr>
+                <a:schemeClr val="accent1"/>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:innerShdw blurRad="114300">
+                <a:schemeClr val="accent1"/>
+              </a:innerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$18:$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Achieving</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Developing</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Exceeding</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Needs Improvement</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Outstanding</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$18:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.9500000000000011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0400000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2000000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-926B-4196-982B-DEEF4D04041B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="164"/>
+        <c:overlap val="-22"/>
+        <c:axId val="749678752"/>
+        <c:axId val="749676352"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="749678752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="749676352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="749676352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="749678752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable1</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1200">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> Performance by Status </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:pattFill prst="ltUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$O$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent1"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent1"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-62DB-4980-8745-0A1F3B09BD6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent2"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent2"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-62DB-4980-8745-0A1F3B09BD6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent3"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-62DB-4980-8745-0A1F3B09BD6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$N$4:$N$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ACTIVE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LEFT</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RESIGNED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$O$4:$O$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>67.972297993574585</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65.922602528522972</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-62DB-4980-8745-0A1F3B09BD6C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="23">
+  <a:schemeClr val="accent3"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="252">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>291042</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>32809</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AADE80A-A905-D22C-341B-C4DCA4D48D70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7936</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>150813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>134936</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBE7D9AB-0878-434C-8A17-5B33A77E8392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>603251</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>22225</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87246FEF-6EFB-42AE-80F3-7E630937F2E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3D6D09E-3F5F-4005-9DF9-387B721D83C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A814349-83B7-45DF-9B89-00A438AF98B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3610,7 +11231,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Performance Band">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Performance Band">
   <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0">
@@ -3826,6 +11447,26 @@
   <dataFields count="1">
     <dataField name="Sum of Eligible_Bonus_Amount" fld="11" baseField="10" baseItem="0"/>
   </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3839,7 +11480,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Employment_Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
   <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0">
@@ -4047,6 +11688,197 @@
   <dataFields count="1">
     <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
   </dataFields>
+  <chartFormats count="17">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4060,7 +11892,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department_Name">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Department_Name">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField dataField="1" showAll="0">
@@ -4280,7 +12112,7 @@
     <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="14">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4289,7 +12121,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -4299,6 +12131,26 @@
       </pivotArea>
     </format>
   </formats>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4312,7 +12164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Department_Name">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Department_Name">
   <location ref="F3:J11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField dataField="1" showAll="0">
@@ -4546,6 +12398,80 @@
   <dataFields count="1">
     <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
   </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="12" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4562,43 +12488,43 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}" name="Table1" displayName="Table1" ref="J1:V151" totalsRowShown="0">
   <autoFilter ref="J1:V151" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="12">
       <calculatedColumnFormula>TRIM(CLEAN(A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="13">
+    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="11">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(B2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="12">
+    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="10">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(C2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" ",TRUE,K2,L2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.XLOOKUP(O2,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="7">
       <calculatedColumnFormula>IFERROR(VLOOKUP(D2,Lookup_Departments!$A$2:$B$7,1,FALSE),"Invalid")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="6">
       <calculatedColumnFormula>IF(ISNUMBER(E2),E2,DATE(RIGHT(E2,4),LEFT(E2,2),MID(E2,4,2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="5">
       <calculatedColumnFormula>DATEDIF(P2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="6">
+    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="4">
       <calculatedColumnFormula>IF(F2="",AVERAGEIF($D$2:$D$151,D2,$F$2:$F$151),F2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="3">
       <calculatedColumnFormula>IF(G2="",AVERAGE($G$2:$G$158),G2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="4">
+    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Amount" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Amount" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="2">
+    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="0">
       <calculatedColumnFormula>TRIM(CLEAN(UPPER(H2)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5208,10 +13134,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0064F973-A037-4303-BA6B-5211153DD9CC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300B5D70-2E1B-495B-8073-3C47A1F580AC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDFAF64-CC90-44C1-8412-C55F11F76DC5}">
   <dimension ref="A1:W158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -17000,7 +24946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -20847,7 +28793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -20917,7 +28863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7B919F-CD76-48B4-ADA5-E710E57B870E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB97C360-6818-46B2-A3F2-70A0EA9CA86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="297">
   <si>
     <t>Emp ID</t>
   </si>
@@ -899,9 +899,6 @@
     <t xml:space="preserve">                        Headcount &amp; Average Salary by Department</t>
   </si>
   <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
     <t>Attrition Rate</t>
   </si>
   <si>
@@ -914,9 +911,6 @@
     <t>Average Perf_Score</t>
   </si>
   <si>
-    <t>Sum of Eligible_Bonus_Amount</t>
-  </si>
-  <si>
     <t>Performance Band</t>
   </si>
   <si>
@@ -924,6 +918,48 @@
   </si>
   <si>
     <t>Bonus Payout</t>
+  </si>
+  <si>
+    <t>Head_Count</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">             </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Headcount by Department</t>
+    </r>
+  </si>
+  <si>
+    <t>Average of Cleaned Salary</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                     </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Average_Salary</t>
+    </r>
+  </si>
+  <si>
+    <t>Count of Cleaned Employment_Status</t>
+  </si>
+  <si>
+    <t>Average of Eligible_Bonus_Amount</t>
   </si>
 </sst>
 </file>
@@ -935,7 +971,7 @@
     <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;₦&quot;#,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -969,6 +1005,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1007,7 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1058,12 +1100,19 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -1123,6 +1172,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFDBEEF4"/>
+      <color rgb="FF31859C"/>
+      <color rgb="FF4F81BD"/>
+      <color rgb="FF000000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1135,451 +1192,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="103"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="3"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable2</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB" sz="1400" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Bonus Payout </a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:pattFill prst="narHorz">
-            <a:fgClr>
-              <a:schemeClr val="accent1"/>
-            </a:fgClr>
-            <a:bgClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="20000"/>
-                <a:lumOff val="80000"/>
-              </a:schemeClr>
-            </a:bgClr>
-          </a:pattFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:innerShdw blurRad="114300">
-              <a:schemeClr val="accent1"/>
-            </a:innerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$B$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:pattFill prst="narHorz">
-              <a:fgClr>
-                <a:schemeClr val="accent1"/>
-              </a:fgClr>
-              <a:bgClr>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="20000"/>
-                  <a:lumOff val="80000"/>
-                </a:schemeClr>
-              </a:bgClr>
-            </a:pattFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:innerShdw blurRad="114300">
-                <a:schemeClr val="accent1"/>
-              </a:innerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-NG"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$A$18:$A$22</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Achieving</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Developing</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Exceeding</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Needs Improvement</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Outstanding</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$B$18:$B$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1.9500000000000011</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0400000000000005</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.7600000000000005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.2000000000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D45C-4DC5-8542-360394E4F62D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="164"/>
-        <c:overlap val="-22"/>
-        <c:axId val="749678752"/>
-        <c:axId val="749676352"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="749678752"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-NG"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="749676352"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="749676352"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="749678752"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-NG"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2890,7 +2502,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3550,6 +3162,133 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3562,11 +3301,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Analysis!$G$3:$G$4</c:f>
+              <c:f>Analysis!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ACTIVE</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3588,405 +3327,51 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-NG"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$F$5:$F$11</c:f>
+              <c:f>Analysis!$F$4:$F$7</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>Finance</c:v>
+                  <c:v>ACTIVE</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Human Resources</c:v>
+                  <c:v>LEFT</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Information Technology</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Operations</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sales</c:v>
+                  <c:v>RESIGNED</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$G$5:$G$11</c:f>
+              <c:f>Analysis!$G$4:$G$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>13</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>22</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C395-491C-ABE9-10BA10D6CFEF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$H$3:$H$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>LEFT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-NG"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$F$5:$F$11</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Finance</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Information Technology</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Operations</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sales</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$H$5:$H$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C395-491C-ABE9-10BA10D6CFEF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$I$3:$I$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>RESIGNED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-NG"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$F$5:$F$11</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Finance</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Information Technology</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Operations</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sales</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$I$5:$I$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C395-491C-ABE9-10BA10D6CFEF}"/>
+              <c16:uniqueId val="{00000003-C395-491C-ABE9-10BA10D6CFEF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -4070,42 +3455,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -4169,7 +3518,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -4182,7 +3530,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4589,22 +3937,22 @@
             <c:numRef>
               <c:f>Analysis!$B$18:$B$22</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1.9500000000000011</c:v>
+                  <c:v>5.0000000000000031E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0400000000000005</c:v>
+                  <c:v>2.0000000000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7600000000000005</c:v>
+                  <c:v>8.0000000000000016E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.2000000000000002</c:v>
+                  <c:v>0.12000000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4684,7 +4032,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4759,7 +4107,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5819,19 +5167,1273 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable4</c:name>
+    <c:fmtId val="22"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Headcount_by</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> Department</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$G$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$18:$F$23</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$G$18:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4892-42F8-AD9D-463A47353394}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="828631456"/>
+        <c:axId val="828630496"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="828631456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="828630496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="828630496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="828631456"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable5</c:name>
+    <c:fmtId val="29"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Average Salary</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$M$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$L$18:$L$23</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$M$18:$M$23</c:f>
+              <c:numCache>
+                <c:formatCode>"₦"#,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>87938.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85649.941176470587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80014.258064516151</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>85508.166666666657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79786.666666666657</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87282.347826086945</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA25-4D39-8313-FF5B52EE3F3F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="417975664"/>
+        <c:axId val="417967024"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="417975664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="417967024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="417967024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;₦&quot;#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="417975664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="23">
   <a:schemeClr val="accent3"/>
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5871,13 +6473,59 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5918,525 +6566,6 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="narHorz">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:innerShdw blurRad="114300">
-          <a:schemeClr val="phClr"/>
-        </a:innerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="narHorz">
-        <a:fgClr>
-          <a:schemeClr val="phClr"/>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:innerShdw blurRad="114300">
-          <a:schemeClr val="phClr"/>
-        </a:innerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6932,7 +7061,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7502,7 +7631,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8021,7 +8150,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="252">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8555,48 +8684,1035 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>587375</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>168275</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>291042</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>32809</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AADE80A-A905-D22C-341B-C4DCA4D48D70}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8748,6 +9864,1881 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B769B0-2F85-43BA-96C8-44A5EC44CF6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>137584</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>74083</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B39458-70CD-4EF7-84D3-B922C7E76B8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>103188</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>373063</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle: Rounded Corners 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DDAA188-FB5F-F03F-35E0-7401946F0F5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="103188" y="119063"/>
+          <a:ext cx="12493625" cy="5246687"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 3202"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>341318</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle: Rounded Corners 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0351F32-BA90-44FE-F064-3CF64066FFA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142880" y="142876"/>
+          <a:ext cx="12422188" cy="587374"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="31859C">
+            <a:alpha val="20000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>                   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>HUMAN RESOURCE ANALYTICS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> AUTOMATED DASHBOARD</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="2800">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>134938</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>365125</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>31752</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7665CBE-5803-F2EE-BDE5-D6C0C422E6D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="127000" y="865188"/>
+          <a:ext cx="2071688" cy="4460877"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="31859C">
+            <a:alpha val="20000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="4F81BD">
+              <a:alpha val="0"/>
+            </a:srgbClr>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>317505</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>31738</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>198441</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>15864</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle: Rounded Corners 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0A922B-C5A9-4DEA-AE7D-369A4C1242F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="317505" y="2039926"/>
+          <a:ext cx="1714499" cy="531813"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="31859C">
+            <a:alpha val="20000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Perfomance_Band</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>79376</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>198436</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>63501</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle: Rounded Corners 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCC946EB-CB39-478A-A94E-22CCE55BAAA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="317500" y="1174751"/>
+          <a:ext cx="1714499" cy="531813"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="31859C">
+            <a:alpha val="20000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>      Department</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>309563</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle: Rounded Corners 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373ABAFA-A904-4274-980E-088124BB58A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="309563" y="2984500"/>
+          <a:ext cx="1714499" cy="531813"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="31859C">
+            <a:alpha val="20000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>        Dataset</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>396868</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>103182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>420681</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>79373</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rectangle: Rounded Corners 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{112FDE49-FF0A-9968-4B79-53135C511D58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2230431" y="1015995"/>
+          <a:ext cx="1857375" cy="706441"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="10196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>596882</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>120636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9507</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>96827</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rectangle: Rounded Corners 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C647C85-17FB-4B58-8E45-3092C5EB786A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4264007" y="1033449"/>
+          <a:ext cx="1857375" cy="706441"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="10196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>217473</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>153967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>241285</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>130158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle: Rounded Corners 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECCFCDDC-995E-4D1D-B9E3-A0A6689B3598}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6329348" y="1066780"/>
+          <a:ext cx="1857375" cy="706441"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="10196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>393698</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171421</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>417511</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>147612</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle: Rounded Corners 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA32F9B8-4C31-482F-AEEA-47F4833BB191}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8339136" y="1084234"/>
+          <a:ext cx="1857375" cy="706441"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="10196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>539747</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>172999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>222247</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle: Rounded Corners 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7848211B-8D31-4F04-BFD6-E5E1094E5830}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10318747" y="1085812"/>
+          <a:ext cx="2127250" cy="723938"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="10196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>63497</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>150807</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>238122</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39682</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle: Rounded Corners 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79C99610-DD4C-C73E-21D1-C6D3E39C8004}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2508247" y="1063620"/>
+          <a:ext cx="1397000" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Total</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Employees</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342888</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>144450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>517513</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>33325</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle: Rounded Corners 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{944E3D32-0176-4607-8478-9AAC27F1AA9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4621201" y="1057263"/>
+          <a:ext cx="1397000" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Average</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Salary</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>373066</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>169843</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>293690</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>63498</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle: Rounded Corners 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1909CA63-5F9D-402C-9BD6-D1E34A72A4B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6484941" y="1082656"/>
+          <a:ext cx="1754187" cy="258780"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Overall Attrition Rate</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>219089</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>4735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>393714</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76172</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle: Rounded Corners 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCA28FF2-19C1-4CF9-9E07-839FC0A07638}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8775714" y="1100110"/>
+          <a:ext cx="1397000" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Total</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Bonus</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>555610</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>180936</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>238110</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Rectangle: Rounded Corners 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1229334-3C44-4F75-B0D8-399F0A827CC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10334610" y="1093749"/>
+          <a:ext cx="2127250" cy="358814"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Average</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1000" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> Years of Services</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-NG" sz="1000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>87309</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95248</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142871</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="Analysis!H7">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Rectangle: Rounded Corners 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D7D92B-A261-E2F9-56BF-EFAE404C2BCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2532059" y="1373186"/>
+          <a:ext cx="1277937" cy="246064"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{97DCB790-AC7E-4E45-AD19-199BF919F77C}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>150</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>287324</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>96830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342886</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>160332</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="Analysis!N24">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Rectangle: Rounded Corners 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55CDCE91-F51B-4629-BF21-47FB090496EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4565637" y="1374768"/>
+          <a:ext cx="1277937" cy="246064"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{B0399A6E-35A4-4FE8-8B63-7E67B1738D88}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>₦506,179.88</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>566740</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>90474</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>11114</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>153976</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="Analysis!L8">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle: Rounded Corners 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0D3116E-00B1-4F58-8F1F-85E0535EC176}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6678615" y="1368412"/>
+          <a:ext cx="1277937" cy="246064"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{0972D65F-6ED0-4DB5-9AE8-833C20EB7220}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>22%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>115891</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>99988</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171453</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>163490</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Rectangle: Rounded Corners 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C50A4C8-2FF2-43FD-A24F-902565513250}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8672516" y="1377926"/>
+          <a:ext cx="1277937" cy="246064"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>301633</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>125386</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>357195</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>6325</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Rectangle: Rounded Corners 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00E2F6A9-DA48-4181-B529-4CD6DB7D80E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10691821" y="1403324"/>
+          <a:ext cx="1277937" cy="246064"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="DBEEF4">
+            <a:alpha val="50196"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:prstClr val="black">
+              <a:alpha val="40000"/>
+            </a:prstClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11231,6 +14222,497 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="Department_Name">
+  <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0">
+      <items count="151">
+        <item x="66"/>
+        <item x="136"/>
+        <item x="121"/>
+        <item x="113"/>
+        <item x="56"/>
+        <item x="91"/>
+        <item x="118"/>
+        <item x="100"/>
+        <item x="109"/>
+        <item x="22"/>
+        <item x="63"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="110"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="61"/>
+        <item x="114"/>
+        <item x="20"/>
+        <item x="10"/>
+        <item x="145"/>
+        <item x="131"/>
+        <item x="45"/>
+        <item x="74"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item x="39"/>
+        <item x="52"/>
+        <item x="71"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="57"/>
+        <item x="84"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="43"/>
+        <item x="134"/>
+        <item x="115"/>
+        <item x="76"/>
+        <item x="72"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="101"/>
+        <item x="69"/>
+        <item x="1"/>
+        <item x="99"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="94"/>
+        <item x="127"/>
+        <item x="25"/>
+        <item x="137"/>
+        <item x="90"/>
+        <item x="125"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="132"/>
+        <item x="128"/>
+        <item x="111"/>
+        <item x="58"/>
+        <item x="82"/>
+        <item x="87"/>
+        <item x="123"/>
+        <item x="68"/>
+        <item x="18"/>
+        <item x="60"/>
+        <item x="37"/>
+        <item x="50"/>
+        <item x="13"/>
+        <item x="102"/>
+        <item x="146"/>
+        <item x="116"/>
+        <item x="83"/>
+        <item x="143"/>
+        <item x="30"/>
+        <item x="44"/>
+        <item x="97"/>
+        <item x="41"/>
+        <item x="49"/>
+        <item x="96"/>
+        <item x="24"/>
+        <item x="70"/>
+        <item x="105"/>
+        <item x="34"/>
+        <item x="77"/>
+        <item x="53"/>
+        <item x="142"/>
+        <item x="130"/>
+        <item x="108"/>
+        <item x="64"/>
+        <item x="104"/>
+        <item x="148"/>
+        <item x="88"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item x="28"/>
+        <item x="140"/>
+        <item x="120"/>
+        <item x="59"/>
+        <item x="149"/>
+        <item x="139"/>
+        <item x="85"/>
+        <item x="35"/>
+        <item x="147"/>
+        <item x="126"/>
+        <item x="17"/>
+        <item x="92"/>
+        <item x="75"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="81"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="141"/>
+        <item x="86"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="122"/>
+        <item x="144"/>
+        <item x="62"/>
+        <item x="78"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="26"/>
+        <item x="133"/>
+        <item x="138"/>
+        <item x="79"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="112"/>
+        <item x="40"/>
+        <item x="31"/>
+        <item x="117"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="47"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="119"/>
+        <item x="65"/>
+        <item x="27"/>
+        <item x="93"/>
+        <item x="135"/>
+        <item x="42"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="29" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23" rowHeaderCaption="Department_Name">
+  <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField dataField="1" showAll="0">
+      <items count="151">
+        <item x="66"/>
+        <item x="136"/>
+        <item x="121"/>
+        <item x="113"/>
+        <item x="56"/>
+        <item x="91"/>
+        <item x="118"/>
+        <item x="100"/>
+        <item x="109"/>
+        <item x="22"/>
+        <item x="63"/>
+        <item x="48"/>
+        <item x="21"/>
+        <item x="110"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="61"/>
+        <item x="114"/>
+        <item x="20"/>
+        <item x="10"/>
+        <item x="145"/>
+        <item x="131"/>
+        <item x="45"/>
+        <item x="74"/>
+        <item x="14"/>
+        <item x="73"/>
+        <item x="39"/>
+        <item x="52"/>
+        <item x="71"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="57"/>
+        <item x="84"/>
+        <item x="98"/>
+        <item x="95"/>
+        <item x="43"/>
+        <item x="134"/>
+        <item x="115"/>
+        <item x="76"/>
+        <item x="72"/>
+        <item x="55"/>
+        <item x="36"/>
+        <item x="101"/>
+        <item x="69"/>
+        <item x="1"/>
+        <item x="99"/>
+        <item x="80"/>
+        <item x="129"/>
+        <item x="94"/>
+        <item x="127"/>
+        <item x="25"/>
+        <item x="137"/>
+        <item x="90"/>
+        <item x="125"/>
+        <item x="32"/>
+        <item x="11"/>
+        <item x="132"/>
+        <item x="128"/>
+        <item x="111"/>
+        <item x="58"/>
+        <item x="82"/>
+        <item x="87"/>
+        <item x="123"/>
+        <item x="68"/>
+        <item x="18"/>
+        <item x="60"/>
+        <item x="37"/>
+        <item x="50"/>
+        <item x="13"/>
+        <item x="102"/>
+        <item x="146"/>
+        <item x="116"/>
+        <item x="83"/>
+        <item x="143"/>
+        <item x="30"/>
+        <item x="44"/>
+        <item x="97"/>
+        <item x="41"/>
+        <item x="49"/>
+        <item x="96"/>
+        <item x="24"/>
+        <item x="70"/>
+        <item x="105"/>
+        <item x="34"/>
+        <item x="77"/>
+        <item x="53"/>
+        <item x="142"/>
+        <item x="130"/>
+        <item x="108"/>
+        <item x="64"/>
+        <item x="104"/>
+        <item x="148"/>
+        <item x="88"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="89"/>
+        <item x="7"/>
+        <item x="28"/>
+        <item x="140"/>
+        <item x="120"/>
+        <item x="59"/>
+        <item x="149"/>
+        <item x="139"/>
+        <item x="85"/>
+        <item x="35"/>
+        <item x="147"/>
+        <item x="126"/>
+        <item x="17"/>
+        <item x="92"/>
+        <item x="75"/>
+        <item x="4"/>
+        <item x="67"/>
+        <item x="81"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="141"/>
+        <item x="86"/>
+        <item x="54"/>
+        <item x="19"/>
+        <item x="122"/>
+        <item x="144"/>
+        <item x="62"/>
+        <item x="78"/>
+        <item x="33"/>
+        <item x="16"/>
+        <item x="0"/>
+        <item x="38"/>
+        <item x="26"/>
+        <item x="133"/>
+        <item x="138"/>
+        <item x="79"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="112"/>
+        <item x="40"/>
+        <item x="31"/>
+        <item x="117"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="47"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="119"/>
+        <item x="65"/>
+        <item x="27"/>
+        <item x="93"/>
+        <item x="135"/>
+        <item x="42"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Head_Count" fld="0" subtotal="count" baseField="4" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="22" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Performance Band">
   <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -11445,18 +14927,14 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Eligible_Bonus_Amount" fld="11" baseField="10" baseItem="0"/>
+    <dataField name="Average of Eligible_Bonus_Amount" fld="11" subtotal="average" baseField="10" baseItem="0" numFmtId="9"/>
   </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
     <chartFormat chart="6" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11479,7 +14957,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
   <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -11688,151 +15166,7 @@
   <dataFields count="1">
     <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
   </dataFields>
-  <chartFormats count="17">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
+  <chartFormats count="4">
     <chartFormat chart="13" format="13" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11891,8 +15225,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Department_Name">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField dataField="1" showAll="0">
@@ -12112,7 +15446,7 @@
     <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="14">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -12121,7 +15455,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12163,11 +15497,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Department_Name">
-  <location ref="F3:J11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Employment_Status">
+  <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
-    <pivotField dataField="1" showAll="0">
+    <pivotField showAll="0">
       <items count="151">
         <item x="66"/>
         <item x="136"/>
@@ -12325,7 +15659,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="7">
         <item x="2"/>
         <item x="5"/>
@@ -12343,7 +15677,7 @@
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
       <items count="4">
         <item x="0"/>
         <item x="1"/>
@@ -12353,35 +15687,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="4"/>
+    <field x="12"/>
   </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="12"/>
-  </colFields>
-  <colItems count="4">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -12394,79 +15702,46 @@
     <i t="grand">
       <x/>
     </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Count of Cleaned Employment_Status" fld="12" subtotal="count" baseField="12" baseItem="0"/>
   </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
+  <chartFormats count="4">
+    <chartFormat chart="7" format="9" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
+        <references count="1">
           <reference field="12" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
+    <chartFormat chart="7" format="10" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
+        <references count="1">
           <reference field="12" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="2" series="1">
+    <chartFormat chart="7" format="11" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
+        <references count="1">
           <reference field="12" count="1" selected="0">
             <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="7" format="6" series="1">
+    <chartFormat chart="7" format="12" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="12" count="1" selected="0">
-            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -12488,43 +15763,43 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}" name="Table1" displayName="Table1" ref="J1:V151" totalsRowShown="0">
   <autoFilter ref="J1:V151" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="14">
       <calculatedColumnFormula>TRIM(CLEAN(A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="11">
+    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="13">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(B2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="12">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(C2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="11">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" ",TRUE,K2,L2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.XLOOKUP(O2,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="7">
+    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="9">
       <calculatedColumnFormula>IFERROR(VLOOKUP(D2,Lookup_Departments!$A$2:$B$7,1,FALSE),"Invalid")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="6">
+    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="8">
       <calculatedColumnFormula>IF(ISNUMBER(E2),E2,DATE(RIGHT(E2,4),LEFT(E2,2),MID(E2,4,2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="7">
       <calculatedColumnFormula>DATEDIF(P2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="6">
       <calculatedColumnFormula>IF(F2="",AVERAGEIF($D$2:$D$151,D2,$F$2:$F$151),F2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="3">
+    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="5">
       <calculatedColumnFormula>IF(G2="",AVERAGE($G$2:$G$158),G2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="2">
+    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Amount" dataDxfId="1">
+    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Amount" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="0">
+    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="2">
       <calculatedColumnFormula>TRIM(CLEAN(UPPER(H2)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12817,19 +16092,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75D2B25-32D9-44F6-8017-10CE3B25D12A}">
-  <dimension ref="A2:O22"/>
+  <dimension ref="A2:O24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.08984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.1796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.6328125" customWidth="1"/>
     <col min="15" max="15" width="17.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -12839,10 +16114,10 @@
         <v>283</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -12856,16 +16131,16 @@
         <v>281</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>284</v>
+        <v>286</v>
+      </c>
+      <c r="G3" t="s">
+        <v>295</v>
       </c>
       <c r="N3" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="O3" t="s">
         <v>287</v>
-      </c>
-      <c r="O3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -12878,20 +16153,11 @@
       <c r="C4" s="10">
         <v>87938.5</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="H4" t="s">
-        <v>266</v>
-      </c>
-      <c r="I4" t="s">
-        <v>267</v>
-      </c>
-      <c r="J4" t="s">
-        <v>280</v>
+      <c r="G4" s="20">
+        <v>117</v>
       </c>
       <c r="N4" s="26" t="s">
         <v>265</v>
@@ -12911,19 +16177,10 @@
         <v>85649.941176470587</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G5" s="20">
-        <v>13</v>
-      </c>
-      <c r="H5" s="20">
-        <v>2</v>
-      </c>
-      <c r="I5" s="20">
-        <v>2</v>
-      </c>
-      <c r="J5" s="20">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N5" s="26" t="s">
         <v>266</v>
@@ -12943,22 +16200,13 @@
         <v>80014.258064516151</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="G6" s="20">
-        <v>16</v>
-      </c>
-      <c r="H6" s="20">
-        <v>1</v>
-      </c>
-      <c r="I6" s="20">
-        <v>1</v>
-      </c>
-      <c r="J6" s="20">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N6" s="26" t="s">
         <v>267</v>
@@ -12967,7 +16215,7 @@
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="26" t="s">
         <v>253</v>
       </c>
@@ -12978,22 +16226,17 @@
         <v>85508.166666666657</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="G7" s="20">
-        <v>28</v>
-      </c>
-      <c r="H7" s="20">
-        <v>3</v>
-      </c>
-      <c r="I7" s="20">
-        <v>5</v>
-      </c>
-      <c r="J7" s="20">
-        <v>36</v>
+        <v>150</v>
+      </c>
+      <c r="H7" s="32">
+        <f>GETPIVOTDATA("Cleaned Employment_Status",$F$3)</f>
+        <v>150</v>
       </c>
       <c r="L7" s="30">
-        <f>(GETPIVOTDATA("Cleaned EMP ID",$F$3,"Cleaned Employment_Status","LEFT")+GETPIVOTDATA("Cleaned EMP ID",$F$3,"Cleaned Employment_Status","RESIGNED"))/GETPIVOTDATA("Cleaned EMP ID",$F$3)</f>
+        <f>(GETPIVOTDATA("Cleaned Employment_Status",$F$3,"Cleaned Employment_Status","LEFT")+GETPIVOTDATA("Cleaned Employment_Status",$F$3,"Cleaned Employment_Status","RESIGNED"))/GETPIVOTDATA("Cleaned Employment_Status",$F$3)</f>
         <v>0.22</v>
       </c>
     </row>
@@ -13007,18 +16250,9 @@
       <c r="C8" s="10">
         <v>79786.666666666657</v>
       </c>
-      <c r="F8" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="20">
-        <v>16</v>
-      </c>
-      <c r="H8" s="20">
-        <v>3</v>
-      </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20">
-        <v>19</v>
+      <c r="L8" s="29">
+        <f>L7</f>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -13031,110 +16265,164 @@
       <c r="C9" s="10">
         <v>87282.347826086945</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" s="20">
-        <v>22</v>
-      </c>
-      <c r="H9" s="20">
-        <v>7</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="F10" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="G10" s="20">
-        <v>22</v>
-      </c>
-      <c r="H10" s="20">
-        <v>7</v>
-      </c>
-      <c r="I10" s="20">
-        <v>2</v>
-      </c>
-      <c r="J10" s="20">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="F11" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="G11" s="20">
-        <v>117</v>
-      </c>
-      <c r="H11" s="20">
-        <v>23</v>
-      </c>
-      <c r="I11" s="20">
-        <v>10</v>
-      </c>
-      <c r="J11" s="20">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="F16" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="L16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>296</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="G17" t="s">
+        <v>291</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="M17" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="B18" s="20">
-        <v>1.9500000000000011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="24">
+        <v>5.0000000000000031E-2</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="G18" s="20">
+        <v>17</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="M18" s="10">
+        <v>87938.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="B19" s="20">
-        <v>1.0400000000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="24">
+        <v>2.0000000000000011E-2</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G19" s="20">
+        <v>18</v>
+      </c>
+      <c r="L19" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="M19" s="10">
+        <v>85649.941176470587</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="B20" s="20">
-        <v>1.7600000000000005</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="24">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G20" s="20">
+        <v>36</v>
+      </c>
+      <c r="L20" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="M20" s="10">
+        <v>80014.258064516151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F21" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="G21" s="20">
+        <v>19</v>
+      </c>
+      <c r="L21" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="M21" s="10">
+        <v>85508.166666666657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B22" s="20">
-        <v>1.2000000000000002</v>
+      <c r="B22" s="24">
+        <v>0.12000000000000002</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G22" s="20">
+        <v>29</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="M22" s="10">
+        <v>79786.666666666657</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F23" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="G23" s="20">
+        <v>31</v>
+      </c>
+      <c r="L23" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="M23" s="10">
+        <v>87282.347826086945</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="M24" s="10">
+        <f>SUM(M18:M23)</f>
+        <v>506179.88040040701</v>
+      </c>
+      <c r="N24" s="10">
+        <f>M24</f>
+        <v>506179.88040040701</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -13154,6 +16442,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464D043E-385C-4EA5-BFC7-4C2AA504AB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA1E6B5-8E15-4898-97CB-DA2D8495374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="6" r:id="rId1"/>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId8"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -983,13 +983,13 @@
     <t>Total_Bonus</t>
   </si>
   <si>
-    <t>Average of Year_of_Service</t>
+    <t>Average Year_of_Service</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
@@ -1007,6 +1007,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1131,225 +1132,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="86">
+  <dxfs count="26">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="&quot;₦&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -1397,24 +1188,99 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <sz val="11"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="4"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FF4F81BD"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <sz val="12"/>
+        <color rgb="FF31859C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF4F81BD"/>
+      </font>
+    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="4" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{F1B4E4D4-7881-425E-8960-774055D62EEF}">
+      <tableStyleElement type="wholeTable" dxfId="25"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 2" pivot="0" table="0" count="0" xr9:uid="{5556B23E-21AB-4165-85A7-BBBBFA797A00}"/>
+    <tableStyle name="Slicer Style 3" pivot="0" table="0" count="1" xr9:uid="{E0ACD3C2-6CF8-4BAC-BD3A-F7DF1EBD72B3}">
+      <tableStyleElement type="wholeTable" dxfId="24"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 4" pivot="0" table="0" count="2" xr9:uid="{16AC44C9-1B35-4F01-9F91-B5681BCDA9F7}">
+      <tableStyleElement type="wholeTable" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FF4F81BD"/>
+      <color rgb="FF31859C"/>
       <color rgb="FFDBEEF4"/>
       <color rgb="FF000000"/>
-      <color rgb="FF31859C"/>
-      <color rgb="FF4F81BD"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 1"/>
+        <x14:slicerStyle name="Slicer Style 2"/>
+        <x14:slicerStyle name="Slicer Style 3"/>
+        <x14:slicerStyle name="Slicer Style 4"/>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -4286,7 +4152,6 @@
               <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -4378,7 +4243,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -10318,7 +10182,7 @@
 </file>
 
 <file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
@@ -15669,89 +15533,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>867833</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>29633</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>92075</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="10" name="Performance_Band">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCECD390-2B26-96E6-7E96-AD5F3C778687}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Performance_Band"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9080500" y="1949450"/>
-              <a:ext cx="1828800" cy="2524125"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-NG" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -15983,7 +15764,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -16088,9 +15869,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="31859C">
-            <a:alpha val="20000"/>
-          </a:srgbClr>
+          <a:srgbClr val="31859C"/>
         </a:solidFill>
         <a:ln>
           <a:noFill/>
@@ -16202,9 +15981,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="31859C">
-            <a:alpha val="20000"/>
-          </a:srgbClr>
+          <a:srgbClr val="31859C"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -16252,18 +16029,19 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>317505</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>31738</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>82538</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>198441</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>15864</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66664</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="Rectangle: Rounded Corners 7">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0A922B-C5A9-4DEA-AE7D-369A4C1242F2}"/>
@@ -16274,8 +16052,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="317505" y="2039926"/>
-          <a:ext cx="1714499" cy="531813"/>
+          <a:off x="317505" y="2368538"/>
+          <a:ext cx="1709736" cy="555626"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -16355,6 +16133,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="10" name="Rectangle: Rounded Corners 9">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCC946EB-CB39-478A-A94E-22CCE55BAAA5}"/>
@@ -16434,18 +16213,19 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>309563</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>190499</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>187325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="12" name="Rectangle: Rounded Corners 11">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373ABAFA-A904-4274-980E-088124BB58A3}"/>
@@ -16456,15 +16236,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="309563" y="2984500"/>
-          <a:ext cx="1714499" cy="531813"/>
+          <a:off x="309563" y="3632200"/>
+          <a:ext cx="1709736" cy="555625"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
           <a:srgbClr val="31859C">
-            <a:alpha val="20000"/>
+            <a:alpha val="89804"/>
           </a:srgbClr>
         </a:solidFill>
         <a:ln>
@@ -17440,6 +17220,17 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>              </a:t>
+          </a:r>
           <a:fld id="{97DCB790-AC7E-4E45-AD19-199BF919F77C}" type="TxLink">
             <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -17449,6 +17240,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="l"/>
             <a:t>150</a:t>
           </a:fld>
           <a:endParaRPr lang="en-NG" sz="1100"/>
@@ -17535,6 +17327,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="l"/>
             <a:t>₦506,179.88</a:t>
           </a:fld>
           <a:endParaRPr lang="en-NG" sz="1100"/>
@@ -17621,6 +17414,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="l"/>
             <a:t>22%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-NG" sz="1100"/>
@@ -17707,6 +17501,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="l"/>
             <a:t>₦496,463.30</a:t>
           </a:fld>
           <a:endParaRPr lang="en-NG" sz="1100"/>
@@ -17793,6 +17588,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="l"/>
             <a:t>6.44</a:t>
           </a:fld>
           <a:endParaRPr lang="en-NG" sz="1100"/>
@@ -18141,7 +17937,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18179,7 +17975,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18217,7 +18013,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18255,7 +18051,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18274,8 +18070,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="45" name="Department_Name 1">
@@ -18298,7 +18094,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -18352,8 +18148,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="46" name="Cleaned Employment_Status 1">
@@ -18376,7 +18172,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -18430,8 +18226,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>165101</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="47" name="Performance_Band 1">
@@ -18454,7 +18250,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -20978,7 +20774,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
   <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21020,16 +20816,16 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="67">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="15">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -21046,644 +20842,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6ACE57F1-1121-49BE-A770-63A5C79D6E65}" name="PivotTable6" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
-  <location ref="A28:A29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField dataField="1" numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="71">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
-  <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="72">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="29" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27" rowHeaderCaption="Department_Name">
-  <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Head_Count" fld="0" subtotal="count" baseField="4" baseItem="1"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="22" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
-  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField dataField="1" numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="10" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="64">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="6" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
-  <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField dataField="1" numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="13" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
-  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-    <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="85">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="84">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
   <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21800,6 +20959,643 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6ACE57F1-1121-49BE-A770-63A5C79D6E65}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+  <location ref="A28:A29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="38" rowHeaderCaption="Department_Name">
+  <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Head_Count" fld="0" subtotal="count" baseField="4" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="22" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
+  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="10" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="18">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="6" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
+  <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="13" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
+  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="20">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
+  <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="29" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Department_Name" xr10:uid="{3B112148-E306-4B09-8CC8-B4A4C081DB54}" sourceName="Department_Name">
   <pivotTables>
@@ -21872,15 +21668,9 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Performance_Band" xr10:uid="{2305E51B-059D-4CDE-A801-0D94794A1F7F}" cache="Slicer_Performance_Band" caption="Performance_Band" rowHeight="241300"/>
-</slicers>
-</file>
-
-<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Department_Name 1" xr10:uid="{3057399E-2EEB-4C29-B1CD-3CCD915A91DA}" cache="Slicer_Department_Name" caption="Department_Name" rowHeight="241300"/>
-  <slicer name="Cleaned Employment_Status 1" xr10:uid="{354F92D9-FABC-46C6-8856-75884730C768}" cache="Slicer_Cleaned_Employment_Status" caption="Cleaned Employment_Status" rowHeight="241300"/>
-  <slicer name="Performance_Band 1" xr10:uid="{CD084D95-A3F3-48C8-92C2-C5D09409DB6D}" cache="Slicer_Performance_Band" caption="Performance_Band" rowHeight="241300"/>
+  <slicer name="Department_Name 1" xr10:uid="{3057399E-2EEB-4C29-B1CD-3CCD915A91DA}" cache="Slicer_Department_Name" caption="Department_Name" style="Slicer Style 4" rowHeight="241300"/>
+  <slicer name="Cleaned Employment_Status 1" xr10:uid="{354F92D9-FABC-46C6-8856-75884730C768}" cache="Slicer_Cleaned_Employment_Status" caption="Cleaned Employment_Status" style="Slicer Style 4" rowHeight="241300"/>
+  <slicer name="Performance_Band 1" xr10:uid="{CD084D95-A3F3-48C8-92C2-C5D09409DB6D}" cache="Slicer_Performance_Band" caption="Performance_Band" style="Slicer Style 4" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -21888,46 +21678,46 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}" name="Table1" displayName="Table1" ref="J1:W151" totalsRowShown="0">
   <autoFilter ref="J1:W151" xr:uid="{D86B9076-85AF-44F4-9A85-F17D0151F005}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{08AF9922-978B-4E5E-B1AD-14907D7F178F}" name="Cleaned EMP ID" dataDxfId="13">
       <calculatedColumnFormula>TRIM(CLEAN(A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="82">
+    <tableColumn id="2" xr3:uid="{8CEE1055-2A2F-4DA0-BEB9-363B105F5B43}" name="Cleaned First_Name" dataDxfId="12">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(B2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="81">
+    <tableColumn id="3" xr3:uid="{1BACBA2A-31FA-4BFA-AC56-8B690BBBE17A}" name="Cleaned Last_Name" dataDxfId="11">
       <calculatedColumnFormula>TRIM(CLEAN(PROPER(C2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="80">
+    <tableColumn id="4" xr3:uid="{ACDDBD44-DED7-45A0-A91C-C301EA2FC8DF}" name="Full_Name" dataDxfId="10">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" ",TRUE,K2,L2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="79">
+    <tableColumn id="5" xr3:uid="{3ACDA19A-4009-42B7-9CEC-E31BB63C9FF9}" name="Department_Name" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(O2,Lookup_Departments!$A$2:$A$7,Lookup_Departments!$B$2:$B$7,"Not Found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="78">
+    <tableColumn id="6" xr3:uid="{DE6D60F7-3EDE-4612-8BF2-B0B2DD1F6F08}" name="Cleaned Dept_Code" dataDxfId="8">
       <calculatedColumnFormula>IFERROR(VLOOKUP(D2,Lookup_Departments!$A$2:$B$7,1,FALSE),"Invalid")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="77">
+    <tableColumn id="7" xr3:uid="{EE50497A-713B-4CF0-BCF5-4B90997B9970}" name="Cleaned Hire_Date" dataDxfId="7">
       <calculatedColumnFormula>IF(ISNUMBER(E2),E2,DATE(RIGHT(E2,4),LEFT(E2,2),MID(E2,4,2)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="76">
+    <tableColumn id="8" xr3:uid="{8900855C-479F-492C-8676-F47182C8617C}" name="Year_of_Service" dataDxfId="6">
       <calculatedColumnFormula>DATEDIF(P2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="75">
+    <tableColumn id="9" xr3:uid="{43DEC46E-02F9-4373-ACF7-EB3138F23FB3}" name="Cleaned Salary" dataDxfId="5">
       <calculatedColumnFormula>IF(F2="",AVERAGEIF($D$2:$D$151,D2,$F$2:$F$151),F2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="74">
+    <tableColumn id="10" xr3:uid="{ACE85FFC-D2E7-4B83-AEB3-D19D39AD1F76}" name="Cleaned Perf_Score" dataDxfId="4">
       <calculatedColumnFormula>IF(G2="",AVERAGE($G$2:$G$158),G2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="73">
+    <tableColumn id="11" xr3:uid="{590E8FC3-346A-46F9-9227-B1111641C818}" name="Performance_Band" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$C$2:$C$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Percentage" dataDxfId="70">
+    <tableColumn id="12" xr3:uid="{17C22A28-ACB1-4EA1-8590-550C4CFACB72}" name="Eligible_Bonus_Percentage" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(S2,Lookup_Performance!$A$2:$A$6,Lookup_Performance!$D$2:$D$6,"Not Found",-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{599D424E-13BE-453F-ACDA-9E66433A137E}" name="Eligible_Bonus_Amount" dataDxfId="68">
+    <tableColumn id="14" xr3:uid="{599D424E-13BE-453F-ACDA-9E66433A137E}" name="Eligible_Bonus_Amount" dataDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[Cleaned Salary]]*Table1[[#This Row],[Eligible_Bonus_Percentage]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="69">
+    <tableColumn id="13" xr3:uid="{15000AA3-E4C9-4C52-A2F3-4B9F18A74F89}" name="Cleaned Employment_Status" dataDxfId="0">
       <calculatedColumnFormula>TRIM(CLEAN(UPPER(H2)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -22226,7 +22016,7 @@
     <col min="1" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.08984375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" bestFit="1" customWidth="1"/>
@@ -22629,14 +22419,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId10"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA1E6B5-8E15-4898-97CB-DA2D8495374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1EE372-7D49-460F-9049-78D95B04557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1188,13 +1188,7 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
@@ -1209,7 +1203,13 @@
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -17221,7 +17221,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -17232,7 +17232,7 @@
             <a:t>              </a:t>
           </a:r>
           <a:fld id="{97DCB790-AC7E-4E45-AD19-199BF919F77C}" type="TxLink">
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -17243,7 +17243,7 @@
             <a:pPr algn="l"/>
             <a:t>150</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-NG" sz="1100"/>
+          <a:endParaRPr lang="en-NG" sz="1200" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -20774,14 +20774,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
-  <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
+  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item x="2"/>
         <item x="5"/>
@@ -20794,8 +20794,8 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField numFmtId="9" showAll="0"/>
@@ -20809,78 +20809,10 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="16">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
-  <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
   <rowFields count="1">
-    <field x="13"/>
+    <field x="4"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
@@ -20890,45 +20822,53 @@
     <i>
       <x v="2"/>
     </i>
-    <i t="grand">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
       <x/>
     </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Cleaned Employment_Status" fld="13" subtotal="count" baseField="12" baseItem="0"/>
+  <dataFields count="2">
+    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
+    <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
   </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="7" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
+  <formats count="2">
+    <format dxfId="15">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="13" count="1" selected="0">
+          <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
           </reference>
         </references>
       </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="11" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
+          <reference field="4294967294" count="1">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="12" series="1">
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -20937,11 +20877,11 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="11" format="14" series="1">
+    <chartFormat chart="6" format="5" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -20959,8 +20899,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6ACE57F1-1121-49BE-A770-63A5C79D6E65}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6ACE57F1-1121-49BE-A770-63A5C79D6E65}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
   <location ref="A28:A29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21005,7 +20945,7 @@
     <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="17">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -21021,114 +20961,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="38" rowHeaderCaption="Department_Name">
-  <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Head_Count" fld="0" subtotal="count" baseField="4" baseItem="1"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="22" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="25" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
   <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21199,7 +21033,7 @@
     <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="10" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="18">
+    <format dxfId="17">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -21253,8 +21087,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
   <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21368,134 +21202,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
-  <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="HeadCount" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-    <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="20">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
   <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21560,7 +21268,7 @@
     <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="21">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -21575,6 +21283,298 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="33" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+  <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="21">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="38" rowHeaderCaption="Department_Name">
+  <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Head_Count" fld="0" subtotal="count" baseField="4" baseItem="1"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="22" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
+  <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Cleaned Employment_Status" fld="13" subtotal="count" baseField="12" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="7" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="14" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1EE372-7D49-460F-9049-78D95B04557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B1FE4E-9304-4F92-9FBD-B0626924D480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="6" r:id="rId1"/>
@@ -1191,7 +1191,13 @@
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
@@ -1203,13 +1209,7 @@
       <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="165" formatCode="&quot;₦&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -2601,6 +2601,1139 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable3</c:name>
+    <c:fmtId val="11"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t> Attrition Rate </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:alpha val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:alpha val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$4:$F$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ACTIVE</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LEFT</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>RESIGNED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$G$4:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9ECA-428B-A005-B963A5DA9F9D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="412426144"/>
+        <c:axId val="412422304"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="412426144"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="412422304"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="412422304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="412426144"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="DBEEF4">
+        <a:alpha val="5098"/>
+      </a:srgbClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7366,6 +8499,270 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$L$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Attrition rate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$L$7:$L$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A664-4331-A51F-8FFA9BAE7CA5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="1728806495"/>
+        <c:axId val="1728801215"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1728806495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1728801215"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1728801215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1728806495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="103"/>
     </mc:Choice>
     <mc:Fallback>
@@ -8244,7 +9641,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8904,1139 +10301,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable3</c:name>
-    <c:fmtId val="11"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t> Attrition Rate </a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="9"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="10"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="11"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="12"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="13"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="14"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$G$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$F$4:$F$7</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>ACTIVE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>LEFT</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>RESIGNED</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$G$4:$G$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>117</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9ECA-428B-A005-B963A5DA9F9D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="65"/>
-        <c:axId val="412426144"/>
-        <c:axId val="412422304"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="412426144"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-NG"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="412422304"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="412422304"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="412426144"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="DBEEF4">
-        <a:alpha val="5098"/>
-      </a:srgbClr>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst>
-      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-        <a:prstClr val="black">
-          <a:alpha val="40000"/>
-        </a:prstClr>
-      </a:outerShdw>
-    </a:effectLst>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-NG"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="23">
   <a:schemeClr val="accent3"/>
@@ -10044,6 +10308,46 @@
 </file>
 
 <file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -10182,12 +10486,6 @@
 </file>
 
 <file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10224,6 +10522,12 @@
     <a:lumMod val="50000"/>
     <a:lumOff val="50000"/>
   </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
 
@@ -10764,6 +11068,576 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13934,1034 +14808,6 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15531,6 +15377,1034 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -15756,6 +16630,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>116416</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>10582</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>560917</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>137582</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13479C65-3C18-4034-B6B1-169D747330EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -20774,6 +21686,176 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
+  <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="14">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="29" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+  <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="17">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -20848,7 +21930,7 @@
     <dataField name="Average Salary" fld="8" subtotal="average" baseField="4" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="15">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -20857,7 +21939,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -20899,7 +21981,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6ACE57F1-1121-49BE-A770-63A5C79D6E65}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
   <location ref="A28:A29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
@@ -20945,7 +22027,7 @@
     <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -20961,418 +22043,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
-  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField dataField="1" numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="10" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="17">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="6" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="24" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
-  <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField dataField="1" numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="13" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6343A1DA-E553-4739-9DC1-7663658B3C83}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="Department_Name">
-  <location ref="L17:M23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Cleaned Salary" fld="8" subtotal="average" baseField="4" baseItem="2" numFmtId="165"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="18">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="29" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="33" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
-  <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="2"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average Year_of_Service" fld="7" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="21">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9766C7AF-3425-454D-9C4E-268C288647D8}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="38" rowHeaderCaption="Department_Name">
   <location ref="F17:G23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -21478,7 +22149,133 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C65AF6F8-97EA-40FE-926F-D435681070FB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28" rowHeaderCaption="Performance Band">
+  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField dataField="1" numFmtId="9" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Eligible_Bonus_Amount" fld="12" baseField="10" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="6" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="24" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
   <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -21579,6 +22376,121 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3D5CA70F-9904-4A47-AFC0-00D008E6E30C}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Employment_Status">
+  <location ref="N3:O6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField numFmtId="9" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average Perf_Score" fld="9" subtotal="average" baseField="12" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="13" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -24482,7 +25394,7 @@
       </c>
       <c r="Q25" s="17">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R25" s="14">
         <f t="shared" si="3"/>
@@ -26196,7 +27108,7 @@
       </c>
       <c r="Q46" s="17">
         <f t="shared" ca="1" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R46" s="14">
         <f t="shared" si="12"/>

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B1FE4E-9304-4F92-9FBD-B0626924D480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ABA0B2-ACAD-4A96-9CE4-E38859542628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2588,7 +2588,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -7218,22 +7217,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+  <c:extLst/>
 </c:chartSpace>
 </file>
 
@@ -21856,7 +21840,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Department_Name">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{95C03F21-8440-4E60-A15F-EDE839858110}" name="Headcount &amp; Average Salary by Department" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16" rowHeaderCaption="Department_Name">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -22276,7 +22260,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12" rowHeaderCaption="Employment_Status">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FEAA84F8-7B84-44FD-A04F-FD9B3F7229C6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Employment_Status">
   <location ref="F3:G7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -22334,7 +22318,7 @@
   <dataFields count="1">
     <dataField name="Count of Cleaned Employment_Status" fld="13" subtotal="count" baseField="12" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="6">
     <chartFormat chart="7" format="9" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -22372,6 +22356,15 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="11" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">

--- a/data/HR_Analytics_Capstone_Raw_Data.xlsx
+++ b/data/HR_Analytics_Capstone_Raw_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\IOTBTECH 2026\Excel Folder\Excel-Capstone-Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ABA0B2-ACAD-4A96-9CE4-E38859542628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2B9658-63DE-485F-A20F-F82B026B3848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2613,6 +2613,666 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable5</c:name>
+    <c:fmtId val="33"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Average Salary</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$M$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-NG"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$L$18:$L$23</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Finance</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Human Resources</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Marketing</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$M$18:$M$23</c:f>
+              <c:numCache>
+                <c:formatCode>"₦"#,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>87938.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85649.941176470587</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80014.258064516151</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>85508.166666666657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79786.666666666657</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87282.347826086945</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9DD9-4107-9EB9-C814B6E93C1C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="417975664"/>
+        <c:axId val="417967024"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="417975664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="417967024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="417967024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;₦&quot;#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="417975664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="DBEEF4">
+        <a:alpha val="5098"/>
+      </a:srgbClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
     <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable3</c:name>
     <c:fmtId val="11"/>
   </c:pivotSource>
@@ -3732,7 +4392,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8747,6 +9407,464 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable8</c:name>
+    <c:fmtId val="33"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Average</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> Tenure</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-NG"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$F$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$F$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$F$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6444-4331-8ACA-6ECA3CAAD2C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1948843487"/>
+        <c:axId val="1948855967"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1948843487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1948855967"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1948855967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-NG"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1948843487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-NG"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="103"/>
     </mc:Choice>
     <mc:Fallback>
@@ -9625,666 +10743,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[HR_Analytics_Capstone_Raw_Data.xlsx]Analysis!PivotTable5</c:name>
-    <c:fmtId val="33"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="1">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Average Salary</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-NG"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$M$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-NG"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$L$18:$L$23</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Finance</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Information Technology</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Marketing</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Operations</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sales</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$M$18:$M$23</c:f>
-              <c:numCache>
-                <c:formatCode>"₦"#,##0.00</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>87938.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>85649.941176470587</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>80014.258064516151</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>85508.166666666657</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>79786.666666666657</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>87282.347826086945</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9DD9-4107-9EB9-C814B6E93C1C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="417975664"/>
-        <c:axId val="417967024"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="417975664"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-NG"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="417967024"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="417967024"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="&quot;₦&quot;#,##0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="417975664"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="DBEEF4">
-        <a:alpha val="5098"/>
-      </a:srgbClr>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst>
-      <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-        <a:prstClr val="black">
-          <a:alpha val="40000"/>
-        </a:prstClr>
-      </a:outerShdw>
-    </a:effectLst>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-NG"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="23">
   <a:schemeClr val="accent3"/>
@@ -10332,6 +10790,46 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -10510,12 +11008,6 @@
 </file>
 
 <file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10552,6 +11044,12 @@
     <a:lumMod val="50000"/>
     <a:lumOff val="50000"/>
   </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
 
@@ -11052,6 +11550,509 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11621,7 +12622,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15362,6 +16363,509 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15886,509 +17390,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -16652,6 +17653,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>179916</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>455083</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>21165</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0B96784-83CD-47DA-944E-1B3FF374F4FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -21772,7 +22811,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30" rowHeaderCaption="">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F4E7B9D-DDA8-4061-9C46-C8585D2A937B}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="34" rowHeaderCaption="">
   <location ref="F28:F29" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -21827,6 +22866,44 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
+  <chartFormats count="4">
+    <chartFormat chart="30" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
